--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3710 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>ACETILSALICILICO ACIDO</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>A.A.S. 100 mg COMPRIMIDOS, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>686580</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>A.A.S. 100 mg COMPRIMIDOS, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=42991</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>ACETILSALICILICO ACIDO</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>A.A.S. 500 mg COMPRIMIDOS , 20 comprimidos</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>700693</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>A.A.S. 500 mg COMPRIMIDOS , 20 comprimidos</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=42956</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr"/>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>PARACETAMOL, FENILEFRINA BITARTRATO, CLORFENAMINA MALEATO</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>ABACAT GRANULADO PARA SOLUCIÓN ORAL. 10 sobres</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>692223</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>ABACAT GRANULADO PARA SOLUCIÓN ORAL. 10 sobres</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76206</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR TARBIS 300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG 60 comprimidos (Blister Al/Al)</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>727637</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR TARBIS 300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG 60 comprimidos (Blister Al/Al)</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=84740</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O101" s="11" t="inlineStr"/>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA  DR. REDDYS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>711415</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA  DR. REDDYS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81012</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O102" s="11" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR SULFATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA AUROVITAS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>715527</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA AUROVITAS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81926</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O103" s="11" t="inlineStr"/>
+      <c r="P103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR CLORHIDRATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA GLENMARK 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos (Blister PVD/PVDC/Al)</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>719707</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA GLENMARK 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos (Blister PVD/PVDC/Al)</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=82591</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR SULFATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA MACLEODS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos (Blister Al/Al)</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>730479</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA MACLEODS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos (Blister Al/Al)</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85810</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR SULFATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TARBIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG , 30 comprimidos (OPA/Al/PVC/Al)</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>733207</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TARBIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG , 30 comprimidos (OPA/Al/PVC/Al)</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86488</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR SULFATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TARBIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG , 30 comprimidos (PVC/PVDC/Al)</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>733208</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TARBIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG , 30 comprimidos (PVC/PVDC/Al)</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86488</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TEVA 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>712262</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA TEVA 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81176</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR SULFATO, LAMIVUDINA</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA VIATRIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>721596</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>ABACAVIR/LAMIVUDINA VIATRIS 600 MG/300 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83074</t>
+        </is>
+      </c>
+      <c r="N109" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O109" s="11" t="inlineStr"/>
+      <c r="P109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>INSULINA GLARGINA</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>ABASAGLAR 100 UNIDADES/ML KWIKPEN SOLUCION INYECTABLE EN PLUMA PRECARGADA  5 plumas precargadas de 3 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>711261</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>ABASAGLAR 100 UNIDADES/ML KWIKPEN SOLUCION INYECTABLE EN PLUMA PRECARGADA  5 plumas precargadas de 3 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114944012</t>
+        </is>
+      </c>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O110" s="11" t="inlineStr"/>
+      <c r="P110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 100 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>765850</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 100 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74124</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 100 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>680816</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 100 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M112" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74124</t>
+        </is>
+      </c>
+      <c r="N112" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O112" s="11" t="inlineStr"/>
+      <c r="P112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 12 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>765846</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 12 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74120</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 12 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>680804</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 12 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74120</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 25 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>765860</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 25 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74121</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 25 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>680807</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 25 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74121</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 50 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>765848</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 50 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74122</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 50 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>680810</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 50 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74122</t>
+        </is>
+      </c>
+      <c r="N118" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="11" t="inlineStr"/>
+      <c r="P118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 75 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>765849</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 75 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 10 parches</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74123</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="11" t="inlineStr"/>
+      <c r="P119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 75 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>680813</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>ABATTRA 75 MICROGRAMOS/HORA PARCHES TRANSDERMICOS EFG, 5 parches</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=74123</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>SILDENAFILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>ABECED 25 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 4 comprimidos</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>763340</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>ABECED 25 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 4 comprimidos</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89032</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>LOPERAMIDA HIDROCLORURO</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>ABECLIN 2 MG COMPRIMIDOS EFG, 20 comprimidos</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>731848</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>ABECLIN 2 MG COMPRIMIDOS EFG, 20 comprimidos</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86274</t>
+        </is>
+      </c>
+      <c r="N122" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>IDECABTAGEN VICLEUCEL</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>ABECMA 260-500 x 10e6 CELULAS DISPERSION PARA PERFUSION, 1 o más bolsas</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>732577</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>ABECMA 260-500 x 10e6 CELULAS DISPERSION PARA PERFUSION, 1 o más bolsas</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211539001</t>
+        </is>
+      </c>
+      <c r="N123" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>AMFOTERICINA B</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>ABELCET COMPLEJO LIPIDICO 5 mg/ml CONCENTRADO PARA DISPERSION PARA PERFUSION , 10 viales de 20 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>681726</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>ABELCET COMPLEJO LIPIDICO 5 mg/ml CONCENTRADO PARA DISPERSION PARA PERFUSION , 10 viales de 20 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M124" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60945</t>
+        </is>
+      </c>
+      <c r="N124" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O124" s="11" t="inlineStr"/>
+      <c r="P124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>BEVACIZUMAB</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>ABEVMY 25 MG/ML CONCENTRADO PARA SOLUCION PARA PERFUSION, 1 vial de 16 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>764395</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>ABEVMY 25 MG/ML CONCENTRADO PARA SOLUCION PARA PERFUSION, 1 vial de 16 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201515001</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>BEVACIZUMAB</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>ABEVMY 25 MG/ML CONCENTRADO PARA SOLUCION PARA PERFUSION, 1 vial de 4 ml</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>764394</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>ABEVMY 25 MG/ML CONCENTRADO PARA SOLUCION PARA PERFUSION, 1 vial de 4 ml</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201515001</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 200 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 15 comprimidos</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>712741</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 200 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 15 comprimidos</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81256</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 200 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>712742</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 200 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81256</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 400 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>712746</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 400 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81257</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 600 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>712749</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 600 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81258</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>FENTANILO CITRATO</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 800 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 15 comprimidos</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>712751</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>ABFENTIQ 800 MICROGRAMOS COMPRIMIDOS PARA CHUPAR EFG 15 comprimidos</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81259</t>
+        </is>
+      </c>
+      <c r="N131" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>FLUOCINOLONA ACETONIDO, FRAMICETINA SULFATO</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>ABICREM 0,25 MG/G +5 MG/G CREMA , 1 tubo de 50 g</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>700286</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>ABICREM 0,25 MG/G +5 MG/G CREMA , 1 tubo de 50 g</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=49840</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr"/>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>ABIES NIGRA GLOBULOS BOIRON, 1 envase de 4g (C5)</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>734308</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>ABIES NIGRA GLOBULOS BOIRON, 1 envase de 4g (C5)</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86829</t>
+        </is>
+      </c>
+      <c r="N133" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P133" s="12" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 1 MG/ML SOLUCION ORAL EFG , 150 ml</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>709769</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 1 MG/ML SOLUCION ORAL EFG , 150 ml</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80580</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 10 MG COMPRIMIDOS BUCODISPERSABLES EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>704003</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 10 MG COMPRIMIDOS BUCODISPERSABLES EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79154</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 10 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>704000</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 10 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79151</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 15 MG COMPRIMIDOS BUCODISPERSABLES EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>704004</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 15 MG COMPRIMIDOS BUCODISPERSABLES EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79155</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 15 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>704001</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 15 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79152</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 30 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>704002</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 30 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79153</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 5 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>703999</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>ABIK 5 MG COMPRIMIDOS EFG , 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79150</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 300 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>701735</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 300 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882001</t>
+        </is>
+      </c>
+      <c r="N141" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr"/>
+      <c r="P141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>701736</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882002</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr"/>
+      <c r="P142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>763460</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882002IP</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
+      <c r="P143" s="11" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>763693</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L144" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882002IP1</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr"/>
+      <c r="P144" s="11" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>768547</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 400 MG POLVO Y DISOLVENTE PARA SUSPENSION INYECTABLE DE LIBERACION PROLONGADA, 1 vial + 1 vial de disolvente</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882002IP2</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL MONOHIDRATO</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 720 MG SUSPENSION INYECTABLE DE LIBERACIÓN PROLONGADA EN JERINGA PRECARGADA, 1 jeringa de 2,4 ml</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>764868</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 720 MG SUSPENSION INYECTABLE DE LIBERACIÓN PROLONGADA EN JERINGA PRECARGADA, 1 jeringa de 2,4 ml</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882009</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL MONOHIDRATO</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 960 MG SUSPENSION INYECTABLE DE LIBERACION PROLONGADA EN JERINGA PRECARGADA, 1 jeringa de 3,2 ml</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>764869</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY MAINTENA 960 MG SUSPENSION INYECTABLE DE LIBERACION PROLONGADA EN JERINGA PRECARGADA, 1 jeringa de 3,2 ml</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113882010</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10768,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +10944,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +10976,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11032,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P147"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10742,6 +10742,3706 @@
       <c r="O147" s="11" t="inlineStr"/>
       <c r="P147" s="11" t="inlineStr"/>
     </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 1 MG/ML SOLUCION ORAL, 1 frasco de 150 ml</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>652738</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 1 MG/ML SOLUCION ORAL, 1 frasco de 150 ml</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K148" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L148" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M148" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276034</t>
+        </is>
+      </c>
+      <c r="N148" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O148" s="11" t="inlineStr"/>
+      <c r="P148" s="11" t="inlineStr"/>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>651608</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J149" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K149" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276025</t>
+        </is>
+      </c>
+      <c r="N149" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O149" s="11" t="inlineStr"/>
+      <c r="P149" s="11" t="inlineStr"/>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>728975</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K150" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L150" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M150" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276025IP</t>
+        </is>
+      </c>
+      <c r="N150" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O150" s="11" t="inlineStr"/>
+      <c r="P150" s="11" t="inlineStr"/>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>720799</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K151" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007IP</t>
+        </is>
+      </c>
+      <c r="N151" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O151" s="11" t="inlineStr"/>
+      <c r="P151" s="11" t="inlineStr"/>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>723945</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H152" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K152" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L152" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M152" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007IP1</t>
+        </is>
+      </c>
+      <c r="N152" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O152" s="11" t="inlineStr"/>
+      <c r="P152" s="11" t="inlineStr"/>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>727740</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K153" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007IP3</t>
+        </is>
+      </c>
+      <c r="N153" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr"/>
+      <c r="P153" s="11" t="inlineStr"/>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>728196</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J154" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K154" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M154" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007</t>
+        </is>
+      </c>
+      <c r="N154" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O154" s="11" t="inlineStr"/>
+      <c r="P154" s="11" t="inlineStr"/>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>765002</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K155" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007IP4</t>
+        </is>
+      </c>
+      <c r="N155" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr"/>
+      <c r="P155" s="11" t="inlineStr"/>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>724618</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 10 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H156" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K156" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L156" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M156" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276007IP2</t>
+        </is>
+      </c>
+      <c r="N156" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O156" s="11" t="inlineStr"/>
+      <c r="P156" s="11" t="inlineStr"/>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>651609</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J157" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K157" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276028</t>
+        </is>
+      </c>
+      <c r="N157" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O157" s="11" t="inlineStr"/>
+      <c r="P157" s="11" t="inlineStr"/>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>728945</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS BUCODISPERSABLES, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J158" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K158" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L158" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M158" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276028IP</t>
+        </is>
+      </c>
+      <c r="N158" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O158" s="11" t="inlineStr"/>
+      <c r="P158" s="11" t="inlineStr"/>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>720815</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H159" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J159" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K159" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276012IP</t>
+        </is>
+      </c>
+      <c r="N159" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr"/>
+      <c r="P159" s="11" t="inlineStr"/>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>727741</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H160" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K160" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L160" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M160" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276012IP3</t>
+        </is>
+      </c>
+      <c r="N160" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O160" s="11" t="inlineStr"/>
+      <c r="P160" s="11" t="inlineStr"/>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>728220</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J161" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K161" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276012</t>
+        </is>
+      </c>
+      <c r="N161" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O161" s="11" t="inlineStr"/>
+      <c r="P161" s="11" t="inlineStr"/>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>732116</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H162" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J162" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K162" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L162" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M162" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276012IP1</t>
+        </is>
+      </c>
+      <c r="N162" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O162" s="11" t="inlineStr"/>
+      <c r="P162" s="11" t="inlineStr"/>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>724543</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J163" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K163" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04278012IP1</t>
+        </is>
+      </c>
+      <c r="N163" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O163" s="11" t="inlineStr"/>
+      <c r="P163" s="11" t="inlineStr"/>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>724619</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 15 mg COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G164" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H164" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J164" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K164" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L164" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M164" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276012 IP2</t>
+        </is>
+      </c>
+      <c r="N164" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O164" s="11" t="inlineStr"/>
+      <c r="P164" s="11" t="inlineStr"/>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 30 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>767415</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 30 MG COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H165" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J165" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K165" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276017IP</t>
+        </is>
+      </c>
+      <c r="N165" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O165" s="11" t="inlineStr"/>
+      <c r="P165" s="11" t="inlineStr"/>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 30 MG COMPRIMIDOS 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>728311</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 30 MG COMPRIMIDOS 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G166" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H166" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J166" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K166" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L166" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M166" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276017</t>
+        </is>
+      </c>
+      <c r="N166" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O166" s="11" t="inlineStr"/>
+      <c r="P166" s="11" t="inlineStr"/>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 5 MG COMPRIMIDOS 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>728154</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 5 MG COMPRIMIDOS 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J167" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K167" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L167" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276002</t>
+        </is>
+      </c>
+      <c r="N167" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O167" s="11" t="inlineStr"/>
+      <c r="P167" s="11" t="inlineStr"/>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 7,5 MG/ML SOLUCION INYECTABLE, 1 vial de 1,3 ml</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>656168</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>ABILIFY 7,5 MG/ML SOLUCION INYECTABLE, 1 vial de 1,3 ml</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H168" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J168" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K168" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L168" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M168" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=04276036</t>
+        </is>
+      </c>
+      <c r="N168" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O168" s="11" t="inlineStr"/>
+      <c r="P168" s="11" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 10 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>762924</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 10 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J169" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K169" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L169" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M169" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88906</t>
+        </is>
+      </c>
+      <c r="N169" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O169" s="11" t="inlineStr"/>
+      <c r="P169" s="11" t="inlineStr"/>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 15 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>762927</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 15 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G170" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H170" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J170" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K170" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L170" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M170" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88907</t>
+        </is>
+      </c>
+      <c r="N170" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O170" s="11" t="inlineStr"/>
+      <c r="P170" s="11" t="inlineStr"/>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 5 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>762920</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>ABILIUM 5 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J171" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K171" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L171" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M171" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88905</t>
+        </is>
+      </c>
+      <c r="N171" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O171" s="11" t="inlineStr"/>
+      <c r="P171" s="11" t="inlineStr"/>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>MOXIFLOXACINO</t>
+        </is>
+      </c>
+      <c r="C172" s="11" t="inlineStr">
+        <is>
+          <t>ABIMOX 5 MG/ML COLIRIO EN SOLUCION , 1 frasco de 5 ml</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>701036</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>ABIMOX 5 MG/ML COLIRIO EN SOLUCION , 1 frasco de 5 ml</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H172" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J172" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K172" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L172" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M172" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78338</t>
+        </is>
+      </c>
+      <c r="N172" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O172" s="11" t="inlineStr"/>
+      <c r="P172" s="11" t="inlineStr"/>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 10 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>761884</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 10 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J173" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L173" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M173" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88580</t>
+        </is>
+      </c>
+      <c r="N173" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O173" s="11" t="inlineStr"/>
+      <c r="P173" s="11" t="inlineStr"/>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 15 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>761887</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 15 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H174" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J174" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K174" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L174" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M174" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88582</t>
+        </is>
+      </c>
+      <c r="N174" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O174" s="11" t="inlineStr"/>
+      <c r="P174" s="11" t="inlineStr"/>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>ARIPIPRAZOL</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 5 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>761883</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>ABIPOL 5 MG CAPSULAS DURAS EFG, 28 cápsulas</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J175" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K175" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L175" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M175" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88579</t>
+        </is>
+      </c>
+      <c r="N175" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O175" s="11" t="inlineStr"/>
+      <c r="P175" s="11" t="inlineStr"/>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C176" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACCORD 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D176" s="11" t="inlineStr">
+        <is>
+          <t>732847</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACCORD 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G176" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H176" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J176" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K176" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L176" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M176" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201512003</t>
+        </is>
+      </c>
+      <c r="N176" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O176" s="11" t="inlineStr"/>
+      <c r="P176" s="11" t="inlineStr"/>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C177" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA CIPLA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>758152</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA CIPLA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H177" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J177" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K177" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L177" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M177" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88033</t>
+        </is>
+      </c>
+      <c r="N177" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O177" s="11" t="inlineStr"/>
+      <c r="P177" s="11" t="inlineStr"/>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C178" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA DR. REDDYS 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="inlineStr">
+        <is>
+          <t>730902</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA DR. REDDYS 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H178" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J178" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K178" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L178" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M178" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85945</t>
+        </is>
+      </c>
+      <c r="N178" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O178" s="11" t="inlineStr"/>
+      <c r="P178" s="11" t="inlineStr"/>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA GLENMARK 250 MG COMPRIMIDOS EFG, 120 comprimidos</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>731609</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA GLENMARK 250 MG COMPRIMIDOS EFG, 120 comprimidos</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H179" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J179" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K179" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L179" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M179" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86189</t>
+        </is>
+      </c>
+      <c r="N179" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O179" s="11" t="inlineStr"/>
+      <c r="P179" s="11" t="inlineStr"/>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C180" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA GLENMARK 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
+        <is>
+          <t>731610</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA GLENMARK 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H180" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J180" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K180" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L180" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M180" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86190</t>
+        </is>
+      </c>
+      <c r="N180" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O180" s="11" t="inlineStr"/>
+      <c r="P180" s="11" t="inlineStr"/>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA KERN PHARMA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>731376</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA KERN PHARMA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H181" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J181" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K181" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L181" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M181" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86095</t>
+        </is>
+      </c>
+      <c r="N181" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O181" s="11" t="inlineStr"/>
+      <c r="P181" s="11" t="inlineStr"/>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA KRKA 500 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
+        <is>
+          <t>731345</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA KRKA 500 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H182" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J182" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K182" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M182" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211553002</t>
+        </is>
+      </c>
+      <c r="N182" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O182" s="11" t="inlineStr"/>
+      <c r="P182" s="11" t="inlineStr"/>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C183" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA MYLAN 1000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>732855</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA MYLAN 1000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H183" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J183" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K183" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L183" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M183" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211571016</t>
+        </is>
+      </c>
+      <c r="N183" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O183" s="11" t="inlineStr"/>
+      <c r="P183" s="11" t="inlineStr"/>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C184" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA NORMON 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D184" s="11" t="inlineStr">
+        <is>
+          <t>758030</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA NORMON 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H184" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J184" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K184" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L184" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M184" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87969</t>
+        </is>
+      </c>
+      <c r="N184" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O184" s="11" t="inlineStr"/>
+      <c r="P184" s="11" t="inlineStr"/>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C185" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA QILU 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>758643</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA QILU 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H185" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I185" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J185" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K185" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L185" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M185" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88188</t>
+        </is>
+      </c>
+      <c r="N185" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O185" s="11" t="inlineStr"/>
+      <c r="P185" s="11" t="inlineStr"/>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C186" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA SANDOZ 500 MG COMPRIMDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos (Al/PVC/PE/PVDC)</t>
+        </is>
+      </c>
+      <c r="D186" s="11" t="inlineStr">
+        <is>
+          <t>731201</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA SANDOZ 500 MG COMPRIMDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos (Al/PVC/PE/PVDC)</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H186" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J186" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K186" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L186" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M186" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86024</t>
+        </is>
+      </c>
+      <c r="N186" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O186" s="11" t="inlineStr"/>
+      <c r="P186" s="11" t="inlineStr"/>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C187" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA STADA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>731230</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA STADA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H187" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J187" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K187" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L187" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M187" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=86037</t>
+        </is>
+      </c>
+      <c r="N187" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O187" s="11" t="inlineStr"/>
+      <c r="P187" s="11" t="inlineStr"/>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TARBIS 250 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 120 comprimidos (HDPE)</t>
+        </is>
+      </c>
+      <c r="D188" s="11" t="inlineStr">
+        <is>
+          <t>763132</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TARBIS 250 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 120 comprimidos (HDPE)</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H188" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K188" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L188" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M188" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88971</t>
+        </is>
+      </c>
+      <c r="N188" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O188" s="11" t="inlineStr"/>
+      <c r="P188" s="11" t="inlineStr"/>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C189" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TARBIS 500 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 60 comprimidos (Al/Al)</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>763134</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TARBIS 500 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 60 comprimidos (Al/Al)</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H189" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I189" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J189" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K189" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L189" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M189" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88972</t>
+        </is>
+      </c>
+      <c r="N189" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O189" s="11" t="inlineStr"/>
+      <c r="P189" s="11" t="inlineStr"/>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C190" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TEVA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D190" s="11" t="inlineStr">
+        <is>
+          <t>757993</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TEVA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G190" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H190" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J190" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K190" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L190" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M190" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87961</t>
+        </is>
+      </c>
+      <c r="N190" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O190" s="11" t="inlineStr"/>
+      <c r="P190" s="11" t="inlineStr"/>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C191" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TRONYL 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>765885</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA TRONYL 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H191" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K191" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L191" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M191" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89854</t>
+        </is>
+      </c>
+      <c r="N191" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O191" s="11" t="inlineStr"/>
+      <c r="P191" s="11" t="inlineStr"/>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C192" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA VIVANTA 250 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 120 comprimidos</t>
+        </is>
+      </c>
+      <c r="D192" s="11" t="inlineStr">
+        <is>
+          <t>767740</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA VIVANTA 250 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 120 comprimidos</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H192" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I192" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J192" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K192" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L192" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M192" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=90340</t>
+        </is>
+      </c>
+      <c r="N192" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O192" s="11" t="inlineStr"/>
+      <c r="P192" s="11" t="inlineStr"/>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C193" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA VIVANTA 500 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>767749</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA VIVANTA 500 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H193" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I193" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J193" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K193" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L193" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M193" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=90341</t>
+        </is>
+      </c>
+      <c r="N193" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O193" s="11" t="inlineStr"/>
+      <c r="P193" s="11" t="inlineStr"/>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ACETATO</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ZENTIVA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="D194" s="11" t="inlineStr">
+        <is>
+          <t>730592</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>ABIRATERONA ZENTIVA 500 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 60 comprimidos</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G194" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H194" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I194" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J194" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K194" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L194" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M194" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85850</t>
+        </is>
+      </c>
+      <c r="N194" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O194" s="11" t="inlineStr"/>
+      <c r="P194" s="11" t="inlineStr"/>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>BILASTINA</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>ABISAX 20 MG COMPRIMIDOS EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>751681</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>ABISAX 20 MG COMPRIMIDOS EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H195" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J195" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K195" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L195" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M195" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87642</t>
+        </is>
+      </c>
+      <c r="N195" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O195" s="11" t="inlineStr"/>
+      <c r="P195" s="11" t="inlineStr"/>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>BRIMONIDINA TARTRATO</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr">
+        <is>
+          <t>ABRADEL 2 MG/ML COLIRIO EN SOLUCION , 1 frasco de 5 ml</t>
+        </is>
+      </c>
+      <c r="D196" s="11" t="inlineStr">
+        <is>
+          <t>696836</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>ABRADEL 2 MG/ML COLIRIO EN SOLUCION , 1 frasco de 5 ml</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H196" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J196" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K196" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L196" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M196" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=77144</t>
+        </is>
+      </c>
+      <c r="N196" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O196" s="11" t="inlineStr"/>
+      <c r="P196" s="11" t="inlineStr"/>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>FLUOCINONIDA, RUSCOGENINA, HEXETIDINA</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>ABRASONE RECTAL, CREMA RECTAL  , 1 tubo de 30 g</t>
+        </is>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>961227</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>ABRASONE RECTAL, CREMA RECTAL  , 1 tubo de 30 g</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H197" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I197" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J197" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K197" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L197" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M197" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=56385</t>
+        </is>
+      </c>
+      <c r="N197" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O197" s="11" t="inlineStr"/>
+      <c r="P197" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10768,7 +14468,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -10944,7 +14643,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -10976,7 +14674,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -11032,7 +14729,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14442,6 +14442,4015 @@
       <c r="O197" s="11" t="inlineStr"/>
       <c r="P197" s="11" t="inlineStr"/>
     </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B198" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D198" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E198" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F198" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G198" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H198" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I198" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J198" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K198" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L198" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M198" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N198" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O198" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P198" s="12" t="inlineStr"/>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E199" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H199" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I199" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J199" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K199" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L199" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M199" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N199" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O199" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P199" s="12" t="inlineStr"/>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E200" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G200" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H200" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I200" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J200" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K200" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L200" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M200" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N200" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O200" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P200" s="12" t="inlineStr"/>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E201" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F201" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G201" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H201" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I201" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J201" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K201" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L201" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M201" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N201" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O201" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P201" s="12" t="inlineStr"/>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D202" s="12" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E202" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F202" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G202" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H202" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I202" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K202" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L202" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M202" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N202" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O202" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P202" s="12" t="inlineStr"/>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>757412</t>
+        </is>
+      </c>
+      <c r="E203" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="F203" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G203" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H203" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I203" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K203" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L203" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M203" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87927</t>
+        </is>
+      </c>
+      <c r="N203" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O203" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P203" s="12" t="inlineStr"/>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO/SALBUTAMOL CIPLA 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D204" s="12" t="inlineStr">
+        <is>
+          <t>716518</t>
+        </is>
+      </c>
+      <c r="E204" s="12" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO/SALBUTAMOL CIPLA 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F204" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G204" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H204" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I204" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K204" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L204" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M204" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=82145</t>
+        </is>
+      </c>
+      <c r="N204" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O204" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P204" s="12" t="inlineStr"/>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B205" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>VENTODUO 100 MICROGRAMOS/50 MICROGRAMOS/PULSACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>700656</t>
+        </is>
+      </c>
+      <c r="E205" s="12" t="inlineStr">
+        <is>
+          <t>VENTODUO 100 MICROGRAMOS/50 MICROGRAMOS/PULSACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F205" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G205" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H205" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I205" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K205" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L205" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M205" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55497</t>
+        </is>
+      </c>
+      <c r="N205" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O205" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P205" s="12" t="inlineStr"/>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B206" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D206" s="12" t="inlineStr">
+        <is>
+          <t>864967</t>
+        </is>
+      </c>
+      <c r="E206" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F206" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G206" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H206" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I206" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K206" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L206" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63011</t>
+        </is>
+      </c>
+      <c r="N206" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P206" s="12" t="inlineStr"/>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C207" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H207" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K207" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L207" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M207" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N207" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O207" s="11" t="inlineStr"/>
+      <c r="P207" s="11" t="inlineStr"/>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D208" s="11" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G208" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H208" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J208" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K208" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L208" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M208" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N208" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O208" s="11" t="inlineStr"/>
+      <c r="P208" s="11" t="inlineStr"/>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H209" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J209" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K209" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L209" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M209" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N209" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O209" s="11" t="inlineStr"/>
+      <c r="P209" s="11" t="inlineStr"/>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D210" s="11" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H210" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J210" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K210" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L210" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M210" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N210" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O210" s="11" t="inlineStr"/>
+      <c r="P210" s="11" t="inlineStr"/>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H211" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J211" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K211" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L211" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M211" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N211" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O211" s="11" t="inlineStr"/>
+      <c r="P211" s="11" t="inlineStr"/>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H212" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J212" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K212" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L212" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M212" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O212" s="11" t="inlineStr"/>
+      <c r="P212" s="11" t="inlineStr"/>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>706160</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J213" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K213" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L213" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M213" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79736</t>
+        </is>
+      </c>
+      <c r="N213" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O213" s="11" t="inlineStr"/>
+      <c r="P213" s="11" t="inlineStr"/>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>ipratropio</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="D214" s="11" t="inlineStr">
+        <is>
+          <t>653830</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H214" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I214" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J214" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K214" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L214" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M214" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67561</t>
+        </is>
+      </c>
+      <c r="N214" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O214" s="11" t="inlineStr"/>
+      <c r="P214" s="11" t="inlineStr"/>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B215" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C215" s="12" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E215" s="12" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F215" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G215" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H215" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I215" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J215" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K215" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L215" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M215" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N215" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O215" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P215" s="12" t="inlineStr"/>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B216" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C216" s="12" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D216" s="12" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E216" s="12" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F216" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G216" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H216" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I216" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J216" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K216" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L216" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M216" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N216" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O216" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P216" s="12" t="inlineStr"/>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B217" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C217" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D217" s="12" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E217" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F217" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G217" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H217" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I217" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J217" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K217" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L217" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M217" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N217" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O217" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P217" s="12" t="inlineStr"/>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B218" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C218" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E218" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F218" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G218" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H218" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I218" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J218" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K218" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L218" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M218" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N218" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O218" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P218" s="12" t="inlineStr"/>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B219" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C219" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D219" s="12" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E219" s="12" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F219" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G219" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H219" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I219" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J219" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K219" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L219" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M219" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N219" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O219" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P219" s="12" t="inlineStr"/>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C220" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>700582</t>
+        </is>
+      </c>
+      <c r="E220" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G220" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H220" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I220" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J220" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K220" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L220" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M220" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76740</t>
+        </is>
+      </c>
+      <c r="N220" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O220" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P220" s="12" t="inlineStr"/>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B221" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C221" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D221" s="12" t="inlineStr">
+        <is>
+          <t>710249</t>
+        </is>
+      </c>
+      <c r="E221" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F221" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H221" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I221" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J221" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K221" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L221" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M221" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80708</t>
+        </is>
+      </c>
+      <c r="N221" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O221" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P221" s="12" t="inlineStr"/>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B222" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C222" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D222" s="12" t="inlineStr">
+        <is>
+          <t>659075</t>
+        </is>
+      </c>
+      <c r="E222" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F222" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G222" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H222" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I222" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J222" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K222" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L222" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M222" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68809</t>
+        </is>
+      </c>
+      <c r="N222" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O222" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P222" s="12" t="inlineStr"/>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B223" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C223" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D223" s="12" t="inlineStr">
+        <is>
+          <t>709802</t>
+        </is>
+      </c>
+      <c r="E223" s="12" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F223" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G223" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H223" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I223" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J223" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K223" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L223" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M223" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80600</t>
+        </is>
+      </c>
+      <c r="N223" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O223" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P223" s="12" t="inlineStr"/>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B224" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C224" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>700581</t>
+        </is>
+      </c>
+      <c r="E224" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F224" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G224" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H224" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I224" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J224" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K224" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L224" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M224" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76713</t>
+        </is>
+      </c>
+      <c r="N224" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O224" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P224" s="12" t="inlineStr"/>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B225" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C225" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>710247</t>
+        </is>
+      </c>
+      <c r="E225" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="F225" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G225" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H225" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I225" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K225" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L225" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M225" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80707</t>
+        </is>
+      </c>
+      <c r="N225" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O225" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P225" s="12" t="inlineStr"/>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B226" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C226" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D226" s="12" t="inlineStr">
+        <is>
+          <t>659065</t>
+        </is>
+      </c>
+      <c r="E226" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G226" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H226" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I226" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K226" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L226" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M226" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68802</t>
+        </is>
+      </c>
+      <c r="N226" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O226" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P226" s="12" t="inlineStr"/>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B227" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C227" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D227" s="12" t="inlineStr">
+        <is>
+          <t>709801</t>
+        </is>
+      </c>
+      <c r="E227" s="12" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F227" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G227" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H227" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I227" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K227" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L227" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M227" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80599</t>
+        </is>
+      </c>
+      <c r="N227" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O227" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P227" s="12" t="inlineStr"/>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B228" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C228" s="12" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="D228" s="12" t="inlineStr">
+        <is>
+          <t>723302</t>
+        </is>
+      </c>
+      <c r="E228" s="12" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="F228" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G228" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H228" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I228" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K228" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L228" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M228" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78813</t>
+        </is>
+      </c>
+      <c r="N228" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O228" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P228" s="12" t="inlineStr"/>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B229" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C229" s="12" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="D229" s="12" t="inlineStr">
+        <is>
+          <t>723299</t>
+        </is>
+      </c>
+      <c r="E229" s="12" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="F229" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G229" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H229" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I229" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K229" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L229" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M229" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78803</t>
+        </is>
+      </c>
+      <c r="N229" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O229" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P229" s="12" t="inlineStr"/>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B230" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C230" s="12" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E230" s="12" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F230" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G230" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H230" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I230" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J230" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K230" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L230" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M230" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N230" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O230" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P230" s="12" t="inlineStr"/>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B231" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>RILAST FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D231" s="12" t="inlineStr">
+        <is>
+          <t>723312</t>
+        </is>
+      </c>
+      <c r="E231" s="12" t="inlineStr">
+        <is>
+          <t>RILAST FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F231" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G231" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H231" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I231" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K231" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L231" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M231" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65045</t>
+        </is>
+      </c>
+      <c r="N231" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O231" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P231" s="12" t="inlineStr"/>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B232" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C232" s="12" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D232" s="12" t="inlineStr">
+        <is>
+          <t>723315</t>
+        </is>
+      </c>
+      <c r="E232" s="12" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F232" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G232" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H232" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I232" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K232" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L232" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M232" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64353</t>
+        </is>
+      </c>
+      <c r="N232" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O232" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P232" s="12" t="inlineStr"/>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B233" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D233" s="12" t="inlineStr">
+        <is>
+          <t>723306</t>
+        </is>
+      </c>
+      <c r="E233" s="12" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F233" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G233" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H233" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I233" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K233" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L233" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M233" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64354</t>
+        </is>
+      </c>
+      <c r="N233" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O233" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P233" s="12" t="inlineStr"/>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D234" s="12" t="inlineStr">
+        <is>
+          <t>723313</t>
+        </is>
+      </c>
+      <c r="E234" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G234" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H234" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I234" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J234" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K234" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L234" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M234" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65044</t>
+        </is>
+      </c>
+      <c r="N234" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O234" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P234" s="12" t="inlineStr"/>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B235" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D235" s="12" t="inlineStr">
+        <is>
+          <t>723314</t>
+        </is>
+      </c>
+      <c r="E235" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F235" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G235" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H235" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I235" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J235" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K235" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L235" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M235" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63958</t>
+        </is>
+      </c>
+      <c r="N235" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O235" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P235" s="12" t="inlineStr"/>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>723311</t>
+        </is>
+      </c>
+      <c r="E236" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G236" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H236" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I236" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J236" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K236" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L236" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63956</t>
+        </is>
+      </c>
+      <c r="N236" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O236" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P236" s="12" t="inlineStr"/>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B237" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D237" s="12" t="inlineStr">
+        <is>
+          <t>723307</t>
+        </is>
+      </c>
+      <c r="E237" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H237" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I237" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J237" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K237" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L237" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M237" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81115</t>
+        </is>
+      </c>
+      <c r="N237" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O237" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P237" s="12" t="inlineStr"/>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C238" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT 80 MICROGRAMOS/2,25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D238" s="12" t="inlineStr">
+        <is>
+          <t>728894</t>
+        </is>
+      </c>
+      <c r="E238" s="12" t="inlineStr">
+        <is>
+          <t>SYMBICORT 80 MICROGRAMOS/2,25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G238" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H238" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I238" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J238" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K238" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L238" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M238" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85232</t>
+        </is>
+      </c>
+      <c r="N238" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O238" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P238" s="12" t="inlineStr"/>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B239" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C239" s="12" t="inlineStr">
+        <is>
+          <t>Trimbow 172 microgramos/5 microgramos/9 microgramos solución para inhalación en envase a presión, 120 dosis</t>
+        </is>
+      </c>
+      <c r="D239" s="12" t="inlineStr">
+        <is>
+          <t>730420</t>
+        </is>
+      </c>
+      <c r="E239" s="12" t="inlineStr">
+        <is>
+          <t>Trimbow 172 microgramos/5 microgramos/9 microgramos solución para inhalación en envase a presión, 120 dosis</t>
+        </is>
+      </c>
+      <c r="F239" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G239" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H239" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I239" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J239" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K239" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L239" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M239" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1171208007</t>
+        </is>
+      </c>
+      <c r="N239" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O239" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P239" s="12" t="inlineStr"/>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>TRIMBOW 87 MICROGRAMOS/5 MICROGRAMOS/9 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D240" s="12" t="inlineStr">
+        <is>
+          <t>718533</t>
+        </is>
+      </c>
+      <c r="E240" s="12" t="inlineStr">
+        <is>
+          <t>TRIMBOW 87 MICROGRAMOS/5 MICROGRAMOS/9 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F240" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G240" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H240" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I240" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J240" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K240" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L240" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M240" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1171208002</t>
+        </is>
+      </c>
+      <c r="N240" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O240" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P240" s="12" t="inlineStr"/>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B241" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 160 microgramos / 4,5 microgramos polvo para inhalacion 120 dosis</t>
+        </is>
+      </c>
+      <c r="D241" s="12" t="inlineStr">
+        <is>
+          <t>723304</t>
+        </is>
+      </c>
+      <c r="E241" s="12" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 160 microgramos / 4,5 microgramos polvo para inhalacion 120 dosis</t>
+        </is>
+      </c>
+      <c r="F241" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H241" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I241" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J241" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K241" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L241" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M241" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114921001</t>
+        </is>
+      </c>
+      <c r="N241" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O241" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P241" s="12" t="inlineStr"/>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B242" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 320 microgramos / 9 microgramos polvo para inhalacion 60 dosis</t>
+        </is>
+      </c>
+      <c r="D242" s="12" t="inlineStr">
+        <is>
+          <t>723305</t>
+        </is>
+      </c>
+      <c r="E242" s="12" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 320 microgramos / 9 microgramos polvo para inhalacion 60 dosis</t>
+        </is>
+      </c>
+      <c r="F242" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G242" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H242" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I242" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J242" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K242" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L242" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M242" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114921004</t>
+        </is>
+      </c>
+      <c r="N242" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O242" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P242" s="12" t="inlineStr"/>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B243" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C243" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D243" s="12" t="inlineStr">
+        <is>
+          <t>723825</t>
+        </is>
+      </c>
+      <c r="E243" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F243" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G243" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H243" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I243" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J243" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K243" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L243" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M243" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N243" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O243" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P243" s="12" t="inlineStr"/>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B244" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="D244" s="12" t="inlineStr">
+        <is>
+          <t>731458</t>
+        </is>
+      </c>
+      <c r="E244" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="F244" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G244" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H244" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I244" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J244" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K244" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L244" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M244" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N244" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O244" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P244" s="12" t="inlineStr"/>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B245" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C245" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D245" s="12" t="inlineStr">
+        <is>
+          <t>730557</t>
+        </is>
+      </c>
+      <c r="E245" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F245" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G245" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H245" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I245" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J245" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K245" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L245" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M245" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85833</t>
+        </is>
+      </c>
+      <c r="N245" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O245" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P245" s="12" t="inlineStr"/>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B246" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 160 MICROGRAMOS/4.5 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 120 dosis</t>
+        </is>
+      </c>
+      <c r="D246" s="12" t="inlineStr">
+        <is>
+          <t>723300</t>
+        </is>
+      </c>
+      <c r="E246" s="12" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 160 MICROGRAMOS/4.5 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 120 dosis</t>
+        </is>
+      </c>
+      <c r="F246" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G246" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H246" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I246" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J246" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K246" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L246" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M246" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78807</t>
+        </is>
+      </c>
+      <c r="N246" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O246" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P246" s="12" t="inlineStr"/>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B247" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C247" s="12" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 320 MICROGRAMOS//9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="D247" s="12" t="inlineStr">
+        <is>
+          <t>723301</t>
+        </is>
+      </c>
+      <c r="E247" s="12" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 320 MICROGRAMOS//9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="F247" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H247" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I247" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J247" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K247" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L247" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M247" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78808</t>
+        </is>
+      </c>
+      <c r="N247" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O247" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P247" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P247"/>
+  <dimension ref="A1:P297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18451,6 +18451,4106 @@
       </c>
       <c r="P247" s="12" t="inlineStr"/>
     </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B248" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C248" s="12" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 160 microgramos/4,5 microgramos polvo para inhalacion 1 inhalador con 120 dosis</t>
+        </is>
+      </c>
+      <c r="D248" s="12" t="inlineStr">
+        <is>
+          <t>723297</t>
+        </is>
+      </c>
+      <c r="E248" s="12" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 160 microgramos/4,5 microgramos polvo para inhalacion 1 inhalador con 120 dosis</t>
+        </is>
+      </c>
+      <c r="F248" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G248" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H248" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I248" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J248" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K248" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L248" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M248" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114920001</t>
+        </is>
+      </c>
+      <c r="N248" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O248" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P248" s="12" t="inlineStr"/>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B249" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C249" s="12" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 320 microgramos/9 microgramos polvo para inhalacion 1 inhalador con 60 dosis</t>
+        </is>
+      </c>
+      <c r="D249" s="12" t="inlineStr">
+        <is>
+          <t>723298</t>
+        </is>
+      </c>
+      <c r="E249" s="12" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 320 microgramos/9 microgramos polvo para inhalacion 1 inhalador con 60 dosis</t>
+        </is>
+      </c>
+      <c r="F249" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G249" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H249" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I249" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J249" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K249" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L249" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M249" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114920004</t>
+        </is>
+      </c>
+      <c r="N249" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O249" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P249" s="12" t="inlineStr"/>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B250" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C250" s="12" t="inlineStr">
+        <is>
+          <t>LUFORBEC 100 MICROGRAMOS/6 MICROGRAMOS/PULSACIÓN SOLUCIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D250" s="12" t="inlineStr">
+        <is>
+          <t>761741</t>
+        </is>
+      </c>
+      <c r="E250" s="12" t="inlineStr">
+        <is>
+          <t>LUFORBEC 100 MICROGRAMOS/6 MICROGRAMOS/PULSACIÓN SOLUCIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F250" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh de 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G250" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H250" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I250" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J250" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K250" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L250" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M250" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88525</t>
+        </is>
+      </c>
+      <c r="N250" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O250" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P250" s="12" t="inlineStr"/>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B251" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C251" s="12" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D251" s="12" t="inlineStr">
+        <is>
+          <t>707896</t>
+        </is>
+      </c>
+      <c r="E251" s="12" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F251" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G251" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H251" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I251" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J251" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K251" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L251" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M251" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80248</t>
+        </is>
+      </c>
+      <c r="N251" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O251" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P251" s="12" t="inlineStr"/>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B252" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C252" s="12" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D252" s="12" t="inlineStr">
+        <is>
+          <t>707904</t>
+        </is>
+      </c>
+      <c r="E252" s="12" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F252" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G252" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H252" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I252" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J252" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K252" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L252" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M252" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80249</t>
+        </is>
+      </c>
+      <c r="N252" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O252" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P252" s="12" t="inlineStr"/>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B253" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C253" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D253" s="12" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E253" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F253" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G253" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H253" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I253" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J253" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K253" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L253" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M253" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N253" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O253" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P253" s="12" t="inlineStr"/>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B254" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C254" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D254" s="12" t="inlineStr">
+        <is>
+          <t>700543</t>
+        </is>
+      </c>
+      <c r="E254" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F254" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G254" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H254" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I254" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J254" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K254" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L254" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M254" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62840</t>
+        </is>
+      </c>
+      <c r="N254" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O254" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P254" s="12" t="inlineStr"/>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B255" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C255" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D255" s="12" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="E255" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F255" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G255" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H255" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I255" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J255" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K255" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L255" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M255" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62841</t>
+        </is>
+      </c>
+      <c r="N255" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O255" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P255" s="12" t="inlineStr"/>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B256" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C256" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D256" s="12" t="inlineStr">
+        <is>
+          <t>816264</t>
+        </is>
+      </c>
+      <c r="E256" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F256" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G256" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H256" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I256" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J256" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K256" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L256" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M256" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63924</t>
+        </is>
+      </c>
+      <c r="N256" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O256" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P256" s="12" t="inlineStr"/>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B257" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C257" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D257" s="12" t="inlineStr">
+        <is>
+          <t>817684</t>
+        </is>
+      </c>
+      <c r="E257" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F257" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G257" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H257" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I257" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J257" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K257" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L257" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M257" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63925</t>
+        </is>
+      </c>
+      <c r="N257" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O257" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P257" s="12" t="inlineStr"/>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B258" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D258" s="12" t="inlineStr">
+        <is>
+          <t>813089</t>
+        </is>
+      </c>
+      <c r="E258" s="12" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G258" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H258" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I258" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J258" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K258" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L258" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M258" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63923</t>
+        </is>
+      </c>
+      <c r="N258" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O258" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P258" s="12" t="inlineStr"/>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B259" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C259" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D259" s="12" t="inlineStr">
+        <is>
+          <t>848671</t>
+        </is>
+      </c>
+      <c r="E259" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F259" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G259" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H259" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I259" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J259" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K259" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L259" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M259" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62867</t>
+        </is>
+      </c>
+      <c r="N259" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O259" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P259" s="12" t="inlineStr"/>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B260" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C260" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D260" s="12" t="inlineStr">
+        <is>
+          <t>700545</t>
+        </is>
+      </c>
+      <c r="E260" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G260" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H260" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I260" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J260" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K260" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L260" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M260" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62868</t>
+        </is>
+      </c>
+      <c r="N260" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O260" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P260" s="12" t="inlineStr"/>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B261" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C261" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D261" s="12" t="inlineStr">
+        <is>
+          <t>700546</t>
+        </is>
+      </c>
+      <c r="E261" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F261" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G261" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H261" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I261" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J261" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K261" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L261" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M261" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62869</t>
+        </is>
+      </c>
+      <c r="N261" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O261" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B262" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C262" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/125 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D262" s="12" t="inlineStr">
+        <is>
+          <t>909820</t>
+        </is>
+      </c>
+      <c r="E262" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/125 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F262" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G262" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H262" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I262" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J262" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K262" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L262" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M262" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64065</t>
+        </is>
+      </c>
+      <c r="N262" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O262" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P262" s="12" t="inlineStr"/>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B263" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C263" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/250 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D263" s="12" t="inlineStr">
+        <is>
+          <t>911610</t>
+        </is>
+      </c>
+      <c r="E263" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/250 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F263" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G263" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H263" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I263" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J263" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K263" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L263" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M263" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64066</t>
+        </is>
+      </c>
+      <c r="N263" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O263" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B264" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C264" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/50 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>906842</t>
+        </is>
+      </c>
+      <c r="E264" s="12" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/50 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G264" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H264" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I264" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J264" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K264" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L264" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M264" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64064</t>
+        </is>
+      </c>
+      <c r="N264" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O264" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P264" s="12" t="inlineStr"/>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B265" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C265" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D265" s="12" t="inlineStr">
+        <is>
+          <t>939959</t>
+        </is>
+      </c>
+      <c r="E265" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F265" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G265" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H265" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I265" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J265" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K265" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L265" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M265" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62842</t>
+        </is>
+      </c>
+      <c r="N265" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O265" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P265" s="12" t="inlineStr"/>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B266" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C266" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D266" s="12" t="inlineStr">
+        <is>
+          <t>940544</t>
+        </is>
+      </c>
+      <c r="E266" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G266" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H266" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I266" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J266" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K266" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L266" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M266" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62843</t>
+        </is>
+      </c>
+      <c r="N266" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O266" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P266" s="12" t="inlineStr"/>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B267" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C267" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D267" s="12" t="inlineStr">
+        <is>
+          <t>940551</t>
+        </is>
+      </c>
+      <c r="E267" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F267" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G267" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H267" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I267" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J267" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K267" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L267" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M267" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62844</t>
+        </is>
+      </c>
+      <c r="N267" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O267" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P267" s="12" t="inlineStr"/>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B268" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C268" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D268" s="12" t="inlineStr">
+        <is>
+          <t>932228</t>
+        </is>
+      </c>
+      <c r="E268" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F268" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G268" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H268" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I268" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J268" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K268" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L268" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M268" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63870</t>
+        </is>
+      </c>
+      <c r="N268" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O268" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P268" s="12" t="inlineStr"/>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B269" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C269" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/250 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D269" s="12" t="inlineStr">
+        <is>
+          <t>932236</t>
+        </is>
+      </c>
+      <c r="E269" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/250 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G269" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H269" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I269" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J269" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K269" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L269" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M269" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63871</t>
+        </is>
+      </c>
+      <c r="N269" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O269" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P269" s="12" t="inlineStr"/>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B270" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C270" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/50 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D270" s="12" t="inlineStr">
+        <is>
+          <t>932178</t>
+        </is>
+      </c>
+      <c r="E270" s="12" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/50 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G270" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H270" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I270" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J270" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K270" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L270" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M270" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63869</t>
+        </is>
+      </c>
+      <c r="N270" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O270" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P270" s="12" t="inlineStr"/>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B271" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C271" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/100 microgramos/inhalación, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D271" s="12" t="inlineStr">
+        <is>
+          <t>804732</t>
+        </is>
+      </c>
+      <c r="E271" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/100 microgramos/inhalación, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F271" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G271" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H271" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I271" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J271" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K271" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L271" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M271" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62667</t>
+        </is>
+      </c>
+      <c r="N271" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O271" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P271" s="12" t="inlineStr"/>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B272" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C272" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D272" s="12" t="inlineStr">
+        <is>
+          <t>700538</t>
+        </is>
+      </c>
+      <c r="E272" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F272" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G272" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H272" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I272" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J272" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K272" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L272" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M272" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62668</t>
+        </is>
+      </c>
+      <c r="N272" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O272" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P272" s="12" t="inlineStr"/>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B273" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C273" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D273" s="12" t="inlineStr">
+        <is>
+          <t>700539</t>
+        </is>
+      </c>
+      <c r="E273" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F273" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G273" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H273" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I273" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J273" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K273" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L273" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M273" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62669</t>
+        </is>
+      </c>
+      <c r="N273" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O273" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P273" s="12" t="inlineStr"/>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B274" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C274" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/125 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D274" s="12" t="inlineStr">
+        <is>
+          <t>874578</t>
+        </is>
+      </c>
+      <c r="E274" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/125 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F274" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G274" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H274" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I274" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J274" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K274" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L274" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M274" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63797</t>
+        </is>
+      </c>
+      <c r="N274" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O274" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P274" s="12" t="inlineStr"/>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B275" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C275" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/250 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D275" s="12" t="inlineStr">
+        <is>
+          <t>874586</t>
+        </is>
+      </c>
+      <c r="E275" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/250 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F275" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G275" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H275" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I275" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J275" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K275" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L275" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M275" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63798</t>
+        </is>
+      </c>
+      <c r="N275" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O275" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P275" s="12" t="inlineStr"/>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B276" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C276" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/50 microgramos/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D276" s="12" t="inlineStr">
+        <is>
+          <t>874354</t>
+        </is>
+      </c>
+      <c r="E276" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/50 microgramos/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F276" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G276" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H276" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I276" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J276" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K276" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L276" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M276" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63796</t>
+        </is>
+      </c>
+      <c r="N276" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O276" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P276" s="12" t="inlineStr"/>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B277" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C277" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D277" s="12" t="inlineStr">
+        <is>
+          <t>730593</t>
+        </is>
+      </c>
+      <c r="E277" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F277" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G277" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H277" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I277" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J277" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K277" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L277" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M277" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85851</t>
+        </is>
+      </c>
+      <c r="N277" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O277" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P277" s="12" t="inlineStr"/>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B278" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C278" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D278" s="12" t="inlineStr">
+        <is>
+          <t>730594</t>
+        </is>
+      </c>
+      <c r="E278" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F278" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G278" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H278" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I278" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J278" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K278" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L278" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M278" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85852</t>
+        </is>
+      </c>
+      <c r="N278" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O278" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P278" s="12" t="inlineStr"/>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B279" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C279" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D279" s="12" t="inlineStr">
+        <is>
+          <t>730595</t>
+        </is>
+      </c>
+      <c r="E279" s="12" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F279" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G279" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H279" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I279" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J279" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K279" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L279" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M279" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85853</t>
+        </is>
+      </c>
+      <c r="N279" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O279" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P279" s="12" t="inlineStr"/>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B280" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C280" s="12" t="inlineStr">
+        <is>
+          <t>FLUSAMIX EASYHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D280" s="12" t="inlineStr">
+        <is>
+          <t>724210</t>
+        </is>
+      </c>
+      <c r="E280" s="12" t="inlineStr">
+        <is>
+          <t>FLUSAMIX EASYHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F280" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G280" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H280" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I280" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J280" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K280" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L280" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M280" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83644</t>
+        </is>
+      </c>
+      <c r="N280" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O280" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P280" s="12" t="inlineStr"/>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B281" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C281" s="12" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D281" s="12" t="inlineStr">
+        <is>
+          <t>730581</t>
+        </is>
+      </c>
+      <c r="E281" s="12" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F281" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G281" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H281" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I281" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J281" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K281" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L281" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M281" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85847</t>
+        </is>
+      </c>
+      <c r="N281" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O281" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P281" s="12" t="inlineStr"/>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B282" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C282" s="12" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D282" s="12" t="inlineStr">
+        <is>
+          <t>730585</t>
+        </is>
+      </c>
+      <c r="E282" s="12" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F282" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G282" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H282" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I282" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J282" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K282" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L282" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M282" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85848</t>
+        </is>
+      </c>
+      <c r="N282" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O282" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P282" s="12" t="inlineStr"/>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B283" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C283" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D283" s="12" t="inlineStr">
+        <is>
+          <t>712329</t>
+        </is>
+      </c>
+      <c r="E283" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F283" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G283" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H283" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I283" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J283" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K283" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L283" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M283" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81181</t>
+        </is>
+      </c>
+      <c r="N283" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O283" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P283" s="12" t="inlineStr"/>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B284" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C284" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/250 MICOGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D284" s="12" t="inlineStr">
+        <is>
+          <t>712330</t>
+        </is>
+      </c>
+      <c r="E284" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/250 MICOGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F284" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G284" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H284" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I284" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J284" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K284" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L284" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M284" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81182</t>
+        </is>
+      </c>
+      <c r="N284" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O284" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P284" s="12" t="inlineStr"/>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B285" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C285" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D285" s="12" t="inlineStr">
+        <is>
+          <t>714997</t>
+        </is>
+      </c>
+      <c r="E285" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F285" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G285" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H285" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I285" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J285" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K285" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L285" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M285" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81790</t>
+        </is>
+      </c>
+      <c r="N285" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O285" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P285" s="12" t="inlineStr"/>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B286" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C286" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D286" s="12" t="inlineStr">
+        <is>
+          <t>715006</t>
+        </is>
+      </c>
+      <c r="E286" s="12" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F286" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G286" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H286" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I286" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J286" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K286" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L286" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M286" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81791</t>
+        </is>
+      </c>
+      <c r="N286" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O286" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P286" s="12" t="inlineStr"/>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B287" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C287" s="12" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12,75 microgramos/100 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D287" s="12" t="inlineStr">
+        <is>
+          <t>730928</t>
+        </is>
+      </c>
+      <c r="E287" s="12" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12,75 microgramos/100 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F287" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G287" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H287" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I287" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J287" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K287" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L287" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M287" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211533001</t>
+        </is>
+      </c>
+      <c r="N287" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O287" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P287" s="12" t="inlineStr"/>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B288" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C288" s="12" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12.75 microgramos/202 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D288" s="12" t="inlineStr">
+        <is>
+          <t>730997</t>
+        </is>
+      </c>
+      <c r="E288" s="12" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12.75 microgramos/202 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F288" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G288" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H288" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I288" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J288" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K288" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L288" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M288" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211533003</t>
+        </is>
+      </c>
+      <c r="N288" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O288" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P288" s="12" t="inlineStr"/>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B289" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C289" s="12" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D289" s="12" t="inlineStr">
+        <is>
+          <t>722187</t>
+        </is>
+      </c>
+      <c r="E289" s="12" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F289" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G289" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H289" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I289" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J289" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K289" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L289" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M289" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83247</t>
+        </is>
+      </c>
+      <c r="N289" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O289" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P289" s="12" t="inlineStr"/>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B290" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C290" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D290" s="12" t="inlineStr">
+        <is>
+          <t>769894</t>
+        </is>
+      </c>
+      <c r="E290" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F290" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G290" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H290" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I290" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J290" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K290" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L290" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M290" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410100C</t>
+        </is>
+      </c>
+      <c r="N290" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O290" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P290" s="12" t="inlineStr"/>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B291" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C291" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D291" s="12" t="inlineStr">
+        <is>
+          <t>763682</t>
+        </is>
+      </c>
+      <c r="E291" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F291" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G291" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H291" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I291" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J291" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K291" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L291" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M291" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8324IP</t>
+        </is>
+      </c>
+      <c r="N291" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O291" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P291" s="12" t="inlineStr"/>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B292" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C292" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D292" s="12" t="inlineStr">
+        <is>
+          <t>769911</t>
+        </is>
+      </c>
+      <c r="E292" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F292" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G292" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H292" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I292" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J292" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K292" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L292" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M292" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=122901</t>
+        </is>
+      </c>
+      <c r="N292" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O292" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P292" s="12" t="inlineStr"/>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B293" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C293" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D293" s="12" t="inlineStr">
+        <is>
+          <t>769013</t>
+        </is>
+      </c>
+      <c r="E293" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F293" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G293" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H293" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I293" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J293" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K293" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L293" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M293" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410200C</t>
+        </is>
+      </c>
+      <c r="N293" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O293" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P293" s="12" t="inlineStr"/>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B294" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C294" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D294" s="12" t="inlineStr">
+        <is>
+          <t>763694</t>
+        </is>
+      </c>
+      <c r="E294" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F294" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G294" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H294" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I294" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J294" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K294" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L294" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M294" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8325IP</t>
+        </is>
+      </c>
+      <c r="N294" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O294" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P294" s="12" t="inlineStr"/>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B295" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C295" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D295" s="12" t="inlineStr">
+        <is>
+          <t>769014</t>
+        </is>
+      </c>
+      <c r="E295" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F295" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G295" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H295" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I295" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J295" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K295" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L295" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M295" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410300C</t>
+        </is>
+      </c>
+      <c r="N295" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O295" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P295" s="12" t="inlineStr"/>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B296" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C296" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D296" s="12" t="inlineStr">
+        <is>
+          <t>763712</t>
+        </is>
+      </c>
+      <c r="E296" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F296" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G296" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H296" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I296" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J296" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K296" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L296" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M296" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8326IP</t>
+        </is>
+      </c>
+      <c r="N296" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O296" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P296" s="12" t="inlineStr"/>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B297" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C297" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION,  SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D297" s="12" t="inlineStr">
+        <is>
+          <t>769640</t>
+        </is>
+      </c>
+      <c r="E297" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION,  SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F297" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G297" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H297" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I297" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J297" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K297" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L297" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M297" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=506780100</t>
+        </is>
+      </c>
+      <c r="N297" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O297" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P297" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P297"/>
+  <dimension ref="A1:P347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22551,6 +22551,3879 @@
       </c>
       <c r="P297" s="12" t="inlineStr"/>
     </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B298" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C298" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D298" s="12" t="inlineStr">
+        <is>
+          <t>763309</t>
+        </is>
+      </c>
+      <c r="E298" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F298" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G298" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H298" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I298" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J298" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K298" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L298" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M298" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=9070IP</t>
+        </is>
+      </c>
+      <c r="N298" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O298" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P298" s="12" t="inlineStr"/>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B299" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C299" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D299" s="12" t="inlineStr">
+        <is>
+          <t>763551</t>
+        </is>
+      </c>
+      <c r="E299" s="12" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F299" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G299" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H299" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I299" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J299" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K299" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L299" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M299" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=9069IP</t>
+        </is>
+      </c>
+      <c r="N299" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O299" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P299" s="12" t="inlineStr"/>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B300" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C300" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D300" s="12" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E300" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F300" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G300" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H300" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I300" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J300" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K300" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L300" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M300" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N300" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O300" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P300" s="12" t="inlineStr"/>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B301" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C301" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D301" s="12" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E301" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F301" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G301" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H301" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I301" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J301" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K301" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L301" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M301" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N301" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O301" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P301" s="12" t="inlineStr"/>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B302" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C302" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D302" s="12" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E302" s="12" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F302" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G302" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H302" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I302" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J302" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K302" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L302" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M302" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N302" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O302" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P302" s="12" t="inlineStr"/>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B303" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C303" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D303" s="12" t="inlineStr">
+        <is>
+          <t>664465</t>
+        </is>
+      </c>
+      <c r="E303" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F303" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G303" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H303" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I303" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J303" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K303" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L303" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M303" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593002</t>
+        </is>
+      </c>
+      <c r="N303" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O303" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P303" s="12" t="inlineStr"/>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B304" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C304" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D304" s="12" t="inlineStr">
+        <is>
+          <t>664467</t>
+        </is>
+      </c>
+      <c r="E304" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F304" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G304" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H304" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I304" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J304" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K304" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L304" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M304" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593007</t>
+        </is>
+      </c>
+      <c r="N304" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O304" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P304" s="12" t="inlineStr"/>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B305" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C305" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D305" s="12" t="inlineStr">
+        <is>
+          <t>728970</t>
+        </is>
+      </c>
+      <c r="E305" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F305" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G305" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H305" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I305" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J305" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K305" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L305" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M305" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439006</t>
+        </is>
+      </c>
+      <c r="N305" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O305" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P305" s="12" t="inlineStr"/>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B306" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C306" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D306" s="12" t="inlineStr">
+        <is>
+          <t>728971</t>
+        </is>
+      </c>
+      <c r="E306" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F306" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G306" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H306" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I306" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J306" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K306" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L306" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M306" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439010</t>
+        </is>
+      </c>
+      <c r="N306" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O306" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P306" s="12" t="inlineStr"/>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B307" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C307" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D307" s="12" t="inlineStr">
+        <is>
+          <t>728969</t>
+        </is>
+      </c>
+      <c r="E307" s="12" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F307" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G307" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H307" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I307" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J307" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K307" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L307" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M307" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439002</t>
+        </is>
+      </c>
+      <c r="N307" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O307" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P307" s="12" t="inlineStr"/>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B308" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C308" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D308" s="12" t="inlineStr">
+        <is>
+          <t>665951</t>
+        </is>
+      </c>
+      <c r="E308" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F308" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G308" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H308" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I308" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J308" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K308" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L308" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M308" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09594002</t>
+        </is>
+      </c>
+      <c r="N308" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O308" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P308" s="12" t="inlineStr"/>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B309" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C309" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D309" s="12" t="inlineStr">
+        <is>
+          <t>665952</t>
+        </is>
+      </c>
+      <c r="E309" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F309" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G309" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H309" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I309" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J309" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K309" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L309" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M309" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09594007</t>
+        </is>
+      </c>
+      <c r="N309" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O309" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P309" s="12" t="inlineStr"/>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B310" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C310" s="12" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D310" s="12" t="inlineStr">
+        <is>
+          <t>665938</t>
+        </is>
+      </c>
+      <c r="E310" s="12" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F310" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G310" s="12" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H310" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I310" s="12" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J310" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K310" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L310" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M310" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09586007</t>
+        </is>
+      </c>
+      <c r="N310" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O310" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P310" s="12" t="inlineStr"/>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B311" s="12" t="inlineStr">
+        <is>
+          <t>olodaterol</t>
+        </is>
+      </c>
+      <c r="C311" s="12" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D311" s="12" t="inlineStr">
+        <is>
+          <t>726795</t>
+        </is>
+      </c>
+      <c r="E311" s="12" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F311" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 5 µg/24h
+D.màx: 5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G311" s="12" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H311" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I311" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J311" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K311" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L311" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M311" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79967</t>
+        </is>
+      </c>
+      <c r="N311" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O311" s="12" t="inlineStr"/>
+      <c r="P311" s="12" t="inlineStr"/>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" s="12" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B312" s="12" t="inlineStr">
+        <is>
+          <t>olodaterol</t>
+        </is>
+      </c>
+      <c r="C312" s="12" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="D312" s="12" t="inlineStr">
+        <is>
+          <t>726790</t>
+        </is>
+      </c>
+      <c r="E312" s="12" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="F312" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 5 µg/24h
+D.màx: 5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G312" s="12" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H312" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I312" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J312" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K312" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L312" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M312" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79966</t>
+        </is>
+      </c>
+      <c r="N312" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O312" s="12" t="inlineStr"/>
+      <c r="P312" s="12" t="inlineStr"/>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B313" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C313" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D313" s="11" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E313" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F313" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G313" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H313" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I313" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J313" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K313" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L313" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M313" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N313" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O313" s="11" t="inlineStr"/>
+      <c r="P313" s="11" t="inlineStr"/>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B314" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D314" s="11" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E314" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F314" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G314" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H314" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I314" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J314" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K314" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L314" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M314" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N314" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O314" s="11" t="inlineStr"/>
+      <c r="P314" s="11" t="inlineStr"/>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B315" s="11" t="inlineStr">
+        <is>
+          <t>glicopirronio</t>
+        </is>
+      </c>
+      <c r="C315" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D315" s="11" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E315" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F315" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G315" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H315" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I315" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J315" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K315" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L315" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M315" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N315" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O315" s="11" t="inlineStr"/>
+      <c r="P315" s="11" t="inlineStr"/>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B316" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C316" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D316" s="11" t="inlineStr">
+        <is>
+          <t>763081</t>
+        </is>
+      </c>
+      <c r="E316" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F316" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G316" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H316" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I316" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J316" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K316" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L316" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M316" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114898002IP</t>
+        </is>
+      </c>
+      <c r="N316" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O316" s="11" t="inlineStr"/>
+      <c r="P316" s="11" t="inlineStr"/>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B317" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C317" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D317" s="11" t="inlineStr">
+        <is>
+          <t>763323</t>
+        </is>
+      </c>
+      <c r="E317" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F317" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G317" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H317" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I317" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J317" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K317" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L317" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M317" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114898002IP1</t>
+        </is>
+      </c>
+      <c r="N317" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O317" s="11" t="inlineStr"/>
+      <c r="P317" s="11" t="inlineStr"/>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B318" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C318" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D318" s="11" t="inlineStr">
+        <is>
+          <t>767476</t>
+        </is>
+      </c>
+      <c r="E318" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F318" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G318" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H318" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I318" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J318" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K318" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L318" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M318" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114898002IP2</t>
+        </is>
+      </c>
+      <c r="N318" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O318" s="11" t="inlineStr"/>
+      <c r="P318" s="11" t="inlineStr"/>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B319" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C319" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D319" s="11" t="inlineStr">
+        <is>
+          <t>768290</t>
+        </is>
+      </c>
+      <c r="E319" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F319" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G319" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H319" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I319" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J319" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K319" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L319" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M319" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114898002IP3</t>
+        </is>
+      </c>
+      <c r="N319" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O319" s="11" t="inlineStr"/>
+      <c r="P319" s="11" t="inlineStr"/>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B320" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C320" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D320" s="11" t="inlineStr">
+        <is>
+          <t>768461</t>
+        </is>
+      </c>
+      <c r="E320" s="11" t="inlineStr">
+        <is>
+          <t>ANORO ELLIPTA 55 MCG/22 MCG POLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F320" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G320" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H320" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I320" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J320" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K320" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L320" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M320" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114898002IP4</t>
+        </is>
+      </c>
+      <c r="N320" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O320" s="11" t="inlineStr"/>
+      <c r="P320" s="11" t="inlineStr"/>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B321" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C321" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D321" s="11" t="inlineStr">
+        <is>
+          <t>769609</t>
+        </is>
+      </c>
+      <c r="E321" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F321" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G321" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H321" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I321" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J321" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K321" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L321" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M321" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP1</t>
+        </is>
+      </c>
+      <c r="N321" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O321" s="11" t="inlineStr"/>
+      <c r="P321" s="11" t="inlineStr"/>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B322" s="11" t="inlineStr">
+        <is>
+          <t>umeclidinio</t>
+        </is>
+      </c>
+      <c r="C322" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D322" s="11" t="inlineStr">
+        <is>
+          <t>768742</t>
+        </is>
+      </c>
+      <c r="E322" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F322" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT — consultar fitxa CIMA</t>
+        </is>
+      </c>
+      <c r="G322" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H322" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I322" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J322" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K322" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L322" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M322" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP</t>
+        </is>
+      </c>
+      <c r="N322" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O322" s="11" t="inlineStr"/>
+      <c r="P322" s="11" t="inlineStr"/>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B323" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C323" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D323" s="12" t="inlineStr">
+        <is>
+          <t>689729</t>
+        </is>
+      </c>
+      <c r="E323" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F323" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G323" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H323" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I323" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J323" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K323" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L323" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M323" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60480</t>
+        </is>
+      </c>
+      <c r="N323" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O323" s="12" t="inlineStr"/>
+      <c r="P323" s="12" t="inlineStr"/>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B324" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C324" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D324" s="12" t="inlineStr">
+        <is>
+          <t>689687</t>
+        </is>
+      </c>
+      <c r="E324" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F324" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G324" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H324" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I324" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J324" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K324" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L324" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M324" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60482</t>
+        </is>
+      </c>
+      <c r="N324" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O324" s="12" t="inlineStr"/>
+      <c r="P324" s="12" t="inlineStr"/>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B325" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C325" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D325" s="12" t="inlineStr">
+        <is>
+          <t>689745</t>
+        </is>
+      </c>
+      <c r="E325" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F325" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G325" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H325" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I325" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J325" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K325" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L325" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M325" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60479</t>
+        </is>
+      </c>
+      <c r="N325" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O325" s="12" t="inlineStr"/>
+      <c r="P325" s="12" t="inlineStr"/>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B326" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C326" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D326" s="12" t="inlineStr">
+        <is>
+          <t>689786</t>
+        </is>
+      </c>
+      <c r="E326" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F326" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G326" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H326" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I326" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J326" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K326" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L326" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M326" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60477</t>
+        </is>
+      </c>
+      <c r="N326" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O326" s="12" t="inlineStr"/>
+      <c r="P326" s="12" t="inlineStr"/>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B327" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C327" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D327" s="12" t="inlineStr">
+        <is>
+          <t>689083</t>
+        </is>
+      </c>
+      <c r="E327" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F327" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G327" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H327" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I327" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J327" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K327" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L327" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M327" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60528</t>
+        </is>
+      </c>
+      <c r="N327" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O327" s="12" t="inlineStr"/>
+      <c r="P327" s="12" t="inlineStr"/>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B328" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C328" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D328" s="12" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E328" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F328" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G328" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H328" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I328" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J328" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K328" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L328" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M328" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N328" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O328" s="12" t="inlineStr"/>
+      <c r="P328" s="12" t="inlineStr"/>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B329" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C329" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D329" s="12" t="inlineStr">
+        <is>
+          <t>689109</t>
+        </is>
+      </c>
+      <c r="E329" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F329" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G329" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H329" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I329" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J329" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K329" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L329" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M329" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60527</t>
+        </is>
+      </c>
+      <c r="N329" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O329" s="12" t="inlineStr"/>
+      <c r="P329" s="12" t="inlineStr"/>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B330" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C330" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D330" s="12" t="inlineStr">
+        <is>
+          <t>689141</t>
+        </is>
+      </c>
+      <c r="E330" s="12" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F330" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G330" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H330" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I330" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J330" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K330" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L330" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M330" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60525</t>
+        </is>
+      </c>
+      <c r="N330" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O330" s="12" t="inlineStr"/>
+      <c r="P330" s="12" t="inlineStr"/>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B331" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C331" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN , 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D331" s="12" t="inlineStr">
+        <is>
+          <t>686139</t>
+        </is>
+      </c>
+      <c r="E331" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN , 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F331" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G331" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H331" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I331" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J331" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K331" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L331" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M331" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60689</t>
+        </is>
+      </c>
+      <c r="N331" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O331" s="12" t="inlineStr"/>
+      <c r="P331" s="12" t="inlineStr"/>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B332" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C332" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D332" s="12" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E332" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F332" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G332" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H332" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I332" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J332" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K332" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L332" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M332" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N332" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O332" s="12" t="inlineStr"/>
+      <c r="P332" s="12" t="inlineStr"/>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B333" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C333" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D333" s="12" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E333" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F333" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G333" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H333" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I333" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J333" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K333" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L333" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M333" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N333" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O333" s="12" t="inlineStr"/>
+      <c r="P333" s="12" t="inlineStr"/>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B334" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C334" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR 50 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D334" s="12" t="inlineStr">
+        <is>
+          <t>686196</t>
+        </is>
+      </c>
+      <c r="E334" s="12" t="inlineStr">
+        <is>
+          <t>INALACOR 50 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F334" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G334" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H334" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I334" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J334" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K334" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L334" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M334" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60686</t>
+        </is>
+      </c>
+      <c r="N334" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O334" s="12" t="inlineStr"/>
+      <c r="P334" s="12" t="inlineStr"/>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B335" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C335" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 184 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D335" s="12" t="inlineStr">
+        <is>
+          <t>700812</t>
+        </is>
+      </c>
+      <c r="E335" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 184 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F335" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G335" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H335" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I335" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J335" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K335" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L335" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M335" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113886005</t>
+        </is>
+      </c>
+      <c r="N335" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O335" s="12" t="inlineStr"/>
+      <c r="P335" s="12" t="inlineStr"/>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B336" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C336" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D336" s="12" t="inlineStr">
+        <is>
+          <t>700811</t>
+        </is>
+      </c>
+      <c r="E336" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F336" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G336" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H336" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I336" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J336" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K336" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L336" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M336" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113886002</t>
+        </is>
+      </c>
+      <c r="N336" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O336" s="12" t="inlineStr"/>
+      <c r="P336" s="12" t="inlineStr"/>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B337" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C337" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 184 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="D337" s="12" t="inlineStr">
+        <is>
+          <t>722406</t>
+        </is>
+      </c>
+      <c r="E337" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 184 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="F337" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G337" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H337" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I337" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J337" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K337" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L337" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M337" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114929005</t>
+        </is>
+      </c>
+      <c r="N337" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O337" s="12" t="inlineStr"/>
+      <c r="P337" s="12" t="inlineStr"/>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B338" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C338" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="D338" s="12" t="inlineStr">
+        <is>
+          <t>722404</t>
+        </is>
+      </c>
+      <c r="E338" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="F338" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G338" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H338" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I338" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J338" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K338" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L338" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M338" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114929002</t>
+        </is>
+      </c>
+      <c r="N338" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O338" s="12" t="inlineStr"/>
+      <c r="P338" s="12" t="inlineStr"/>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B339" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C339" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D339" s="12" t="inlineStr">
+        <is>
+          <t>662361</t>
+        </is>
+      </c>
+      <c r="E339" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F339" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G339" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H339" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I339" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J339" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K339" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L339" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M339" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61971</t>
+        </is>
+      </c>
+      <c r="N339" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O339" s="12" t="inlineStr"/>
+      <c r="P339" s="12" t="inlineStr"/>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B340" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C340" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D340" s="12" t="inlineStr">
+        <is>
+          <t>662353</t>
+        </is>
+      </c>
+      <c r="E340" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F340" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G340" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H340" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I340" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J340" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K340" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L340" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M340" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61972</t>
+        </is>
+      </c>
+      <c r="N340" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O340" s="12" t="inlineStr"/>
+      <c r="P340" s="12" t="inlineStr"/>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B341" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C341" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D341" s="12" t="inlineStr">
+        <is>
+          <t>665562</t>
+        </is>
+      </c>
+      <c r="E341" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F341" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G341" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H341" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I341" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J341" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K341" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L341" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M341" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61788</t>
+        </is>
+      </c>
+      <c r="N341" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O341" s="12" t="inlineStr"/>
+      <c r="P341" s="12" t="inlineStr"/>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B342" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C342" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA 50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D342" s="12" t="inlineStr">
+        <is>
+          <t>665570</t>
+        </is>
+      </c>
+      <c r="E342" s="12" t="inlineStr">
+        <is>
+          <t>TRIALONA 50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F342" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G342" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H342" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I342" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J342" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K342" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L342" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M342" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61787</t>
+        </is>
+      </c>
+      <c r="N342" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O342" s="12" t="inlineStr"/>
+      <c r="P342" s="12" t="inlineStr"/>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B343" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C343" s="12" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 0,25 MG/ ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D343" s="12" t="inlineStr">
+        <is>
+          <t>726516</t>
+        </is>
+      </c>
+      <c r="E343" s="12" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 0,25 MG/ ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F343" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G343" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H343" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I343" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J343" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K343" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L343" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M343" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=84405</t>
+        </is>
+      </c>
+      <c r="N343" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O343" s="12" t="inlineStr"/>
+      <c r="P343" s="12" t="inlineStr"/>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B344" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C344" s="12" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 1 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D344" s="12" t="inlineStr">
+        <is>
+          <t>726517</t>
+        </is>
+      </c>
+      <c r="E344" s="12" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 1 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F344" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G344" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H344" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I344" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J344" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K344" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L344" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M344" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=84406</t>
+        </is>
+      </c>
+      <c r="N344" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O344" s="12" t="inlineStr"/>
+      <c r="P344" s="12" t="inlineStr"/>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B345" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C345" s="12" t="inlineStr">
+        <is>
+          <t>ICSORI 125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D345" s="12" t="inlineStr">
+        <is>
+          <t>705031</t>
+        </is>
+      </c>
+      <c r="E345" s="12" t="inlineStr">
+        <is>
+          <t>ICSORI 125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F345" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G345" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H345" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I345" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J345" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K345" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L345" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M345" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79477</t>
+        </is>
+      </c>
+      <c r="N345" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O345" s="12" t="inlineStr"/>
+      <c r="P345" s="12" t="inlineStr"/>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B346" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C346" s="12" t="inlineStr">
+        <is>
+          <t>ICSORI 250 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D346" s="12" t="inlineStr">
+        <is>
+          <t>705033</t>
+        </is>
+      </c>
+      <c r="E346" s="12" t="inlineStr">
+        <is>
+          <t>ICSORI 250 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F346" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G346" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H346" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I346" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J346" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K346" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L346" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M346" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79478</t>
+        </is>
+      </c>
+      <c r="N346" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O346" s="12" t="inlineStr"/>
+      <c r="P346" s="12" t="inlineStr"/>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B347" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C347" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOSPOLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D347" s="12" t="inlineStr">
+        <is>
+          <t>725109</t>
+        </is>
+      </c>
+      <c r="E347" s="12" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOSPOLVO PARA INHALACION (UNIDOSIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F347" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G347" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H347" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I347" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J347" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K347" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L347" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M347" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=13886002IP1</t>
+        </is>
+      </c>
+      <c r="N347" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O347" s="12" t="inlineStr"/>
+      <c r="P347" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P347"/>
+  <dimension ref="A1:P375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26424,6 +26424,2202 @@
       <c r="O347" s="12" t="inlineStr"/>
       <c r="P347" s="12" t="inlineStr"/>
     </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B348" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C348" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="D348" s="12" t="inlineStr">
+        <is>
+          <t>768316</t>
+        </is>
+      </c>
+      <c r="E348" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="F348" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G348" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H348" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I348" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J348" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K348" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L348" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M348" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114929002IP</t>
+        </is>
+      </c>
+      <c r="N348" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O348" s="12" t="inlineStr"/>
+      <c r="P348" s="12" t="inlineStr"/>
+    </row>
+    <row r="349" ht="40" customHeight="1">
+      <c r="A349" s="12" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B349" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C349" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="D349" s="12" t="inlineStr">
+        <is>
+          <t>769953</t>
+        </is>
+      </c>
+      <c r="E349" s="12" t="inlineStr">
+        <is>
+          <t>REVINTY ELLIPTA 92 MICROGRAMOS/22 MICROGRAMOS POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 30 dosis</t>
+        </is>
+      </c>
+      <c r="F349" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G349" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H349" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I349" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J349" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K349" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L349" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M349" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114929002IP1</t>
+        </is>
+      </c>
+      <c r="N349" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O349" s="12" t="inlineStr"/>
+      <c r="P349" s="12" t="inlineStr"/>
+    </row>
+    <row r="350" ht="40" customHeight="1">
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B350" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C350" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D350" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E350" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F350" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G350" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H350" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I350" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J350" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K350" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L350" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M350" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N350" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O350" s="12" t="inlineStr"/>
+      <c r="P350" s="12" t="inlineStr"/>
+    </row>
+    <row r="351" ht="40" customHeight="1">
+      <c r="A351" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B351" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C351" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D351" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E351" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F351" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G351" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H351" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I351" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J351" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K351" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L351" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M351" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N351" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O351" s="12" t="inlineStr"/>
+      <c r="P351" s="12" t="inlineStr"/>
+    </row>
+    <row r="352" ht="40" customHeight="1">
+      <c r="A352" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B352" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C352" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D352" s="12" t="inlineStr">
+        <is>
+          <t>725241</t>
+        </is>
+      </c>
+      <c r="E352" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F352" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G352" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H352" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I352" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J352" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K352" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L352" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M352" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83987</t>
+        </is>
+      </c>
+      <c r="N352" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O352" s="12" t="inlineStr"/>
+      <c r="P352" s="12" t="inlineStr"/>
+    </row>
+    <row r="353" ht="40" customHeight="1">
+      <c r="A353" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B353" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C353" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D353" s="12" t="inlineStr">
+        <is>
+          <t>672718</t>
+        </is>
+      </c>
+      <c r="E353" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F353" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G353" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H353" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I353" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J353" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K353" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L353" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M353" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N353" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O353" s="12" t="inlineStr"/>
+      <c r="P353" s="12" t="inlineStr"/>
+    </row>
+    <row r="354" ht="40" customHeight="1">
+      <c r="A354" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B354" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C354" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D354" s="12" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E354" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F354" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G354" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H354" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I354" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J354" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K354" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L354" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M354" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N354" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O354" s="12" t="inlineStr"/>
+      <c r="P354" s="12" t="inlineStr"/>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B355" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C355" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D355" s="12" t="inlineStr">
+        <is>
+          <t>668905</t>
+        </is>
+      </c>
+      <c r="E355" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F355" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G355" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H355" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I355" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J355" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K355" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L355" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M355" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61663</t>
+        </is>
+      </c>
+      <c r="N355" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O355" s="12" t="inlineStr"/>
+      <c r="P355" s="12" t="inlineStr"/>
+    </row>
+    <row r="356" ht="40" customHeight="1">
+      <c r="A356" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B356" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C356" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D356" s="12" t="inlineStr">
+        <is>
+          <t>660910</t>
+        </is>
+      </c>
+      <c r="E356" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F356" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G356" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H356" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I356" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J356" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K356" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L356" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M356" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62046</t>
+        </is>
+      </c>
+      <c r="N356" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O356" s="12" t="inlineStr"/>
+      <c r="P356" s="12" t="inlineStr"/>
+    </row>
+    <row r="357" ht="40" customHeight="1">
+      <c r="A357" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B357" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C357" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D357" s="12" t="inlineStr">
+        <is>
+          <t>651927</t>
+        </is>
+      </c>
+      <c r="E357" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F357" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G357" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H357" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I357" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J357" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K357" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L357" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M357" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59254</t>
+        </is>
+      </c>
+      <c r="N357" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O357" s="12" t="inlineStr"/>
+      <c r="P357" s="12" t="inlineStr"/>
+    </row>
+    <row r="358" ht="40" customHeight="1">
+      <c r="A358" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B358" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C358" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D358" s="12" t="inlineStr">
+        <is>
+          <t>885640</t>
+        </is>
+      </c>
+      <c r="E358" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F358" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G358" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H358" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I358" s="12" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J358" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K358" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L358" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M358" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59255</t>
+        </is>
+      </c>
+      <c r="N358" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O358" s="12" t="inlineStr"/>
+      <c r="P358" s="12" t="inlineStr"/>
+    </row>
+    <row r="359" ht="40" customHeight="1">
+      <c r="A359" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B359" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C359" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D359" s="12" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E359" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F359" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G359" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H359" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I359" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J359" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K359" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L359" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M359" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N359" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O359" s="12" t="inlineStr"/>
+      <c r="P359" s="12" t="inlineStr"/>
+    </row>
+    <row r="360" ht="40" customHeight="1">
+      <c r="A360" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B360" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C360" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D360" s="12" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E360" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F360" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G360" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H360" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I360" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J360" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K360" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L360" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M360" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N360" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O360" s="12" t="inlineStr"/>
+      <c r="P360" s="12" t="inlineStr"/>
+    </row>
+    <row r="361" ht="40" customHeight="1">
+      <c r="A361" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B361" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C361" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D361" s="12" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E361" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F361" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G361" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H361" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I361" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J361" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K361" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L361" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M361" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N361" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O361" s="12" t="inlineStr"/>
+      <c r="P361" s="12" t="inlineStr"/>
+    </row>
+    <row r="362" ht="40" customHeight="1">
+      <c r="A362" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B362" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C362" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D362" s="12" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E362" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F362" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G362" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H362" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I362" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J362" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K362" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L362" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M362" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N362" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O362" s="12" t="inlineStr"/>
+      <c r="P362" s="12" t="inlineStr"/>
+    </row>
+    <row r="363" ht="40" customHeight="1">
+      <c r="A363" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B363" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C363" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D363" s="12" t="inlineStr">
+        <is>
+          <t>650966</t>
+        </is>
+      </c>
+      <c r="E363" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F363" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G363" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H363" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I363" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J363" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K363" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L363" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M363" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66670</t>
+        </is>
+      </c>
+      <c r="N363" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O363" s="12" t="inlineStr"/>
+      <c r="P363" s="12" t="inlineStr"/>
+    </row>
+    <row r="364" ht="40" customHeight="1">
+      <c r="A364" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B364" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C364" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D364" s="12" t="inlineStr">
+        <is>
+          <t>650965</t>
+        </is>
+      </c>
+      <c r="E364" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F364" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G364" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H364" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I364" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J364" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K364" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L364" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M364" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66669</t>
+        </is>
+      </c>
+      <c r="N364" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O364" s="12" t="inlineStr"/>
+      <c r="P364" s="12" t="inlineStr"/>
+    </row>
+    <row r="365" ht="40" customHeight="1">
+      <c r="A365" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B365" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C365" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D365" s="12" t="inlineStr">
+        <is>
+          <t>650967</t>
+        </is>
+      </c>
+      <c r="E365" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F365" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G365" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H365" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I365" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J365" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K365" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L365" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M365" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66671</t>
+        </is>
+      </c>
+      <c r="N365" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O365" s="12" t="inlineStr"/>
+      <c r="P365" s="12" t="inlineStr"/>
+    </row>
+    <row r="366" ht="40" customHeight="1">
+      <c r="A366" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B366" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C366" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D366" s="12" t="inlineStr">
+        <is>
+          <t>656614</t>
+        </is>
+      </c>
+      <c r="E366" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F366" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G366" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H366" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I366" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J366" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K366" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L366" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M366" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59036</t>
+        </is>
+      </c>
+      <c r="N366" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O366" s="12" t="inlineStr"/>
+      <c r="P366" s="12" t="inlineStr"/>
+    </row>
+    <row r="367" ht="40" customHeight="1">
+      <c r="A367" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B367" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C367" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D367" s="12" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="E367" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F367" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G367" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H367" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I367" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J367" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K367" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L367" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M367" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N367" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O367" s="12" t="inlineStr"/>
+      <c r="P367" s="12" t="inlineStr"/>
+    </row>
+    <row r="368" ht="40" customHeight="1">
+      <c r="A368" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B368" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C368" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D368" s="12" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E368" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F368" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G368" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H368" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I368" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J368" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K368" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L368" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M368" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N368" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O368" s="12" t="inlineStr"/>
+      <c r="P368" s="12" t="inlineStr"/>
+    </row>
+    <row r="369" ht="40" customHeight="1">
+      <c r="A369" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B369" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C369" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D369" s="12" t="inlineStr">
+        <is>
+          <t>945436</t>
+        </is>
+      </c>
+      <c r="E369" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F369" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G369" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H369" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I369" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J369" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K369" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L369" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M369" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65536</t>
+        </is>
+      </c>
+      <c r="N369" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O369" s="12" t="inlineStr"/>
+      <c r="P369" s="12" t="inlineStr"/>
+    </row>
+    <row r="370" ht="40" customHeight="1">
+      <c r="A370" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B370" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C370" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D370" s="12" t="inlineStr">
+        <is>
+          <t>652283</t>
+        </is>
+      </c>
+      <c r="E370" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F370" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G370" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H370" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I370" s="12" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J370" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K370" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L370" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M370" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67103</t>
+        </is>
+      </c>
+      <c r="N370" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O370" s="12" t="inlineStr"/>
+      <c r="P370" s="12" t="inlineStr"/>
+    </row>
+    <row r="371" ht="40" customHeight="1">
+      <c r="A371" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B371" s="12" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C371" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D371" s="12" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E371" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F371" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G371" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H371" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I371" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J371" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K371" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L371" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M371" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N371" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O371" s="12" t="inlineStr"/>
+      <c r="P371" s="12" t="inlineStr"/>
+    </row>
+    <row r="372" ht="40" customHeight="1">
+      <c r="A372" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B372" s="12" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C372" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D372" s="12" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E372" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F372" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G372" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H372" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I372" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J372" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K372" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L372" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M372" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N372" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O372" s="12" t="inlineStr"/>
+      <c r="P372" s="12" t="inlineStr"/>
+    </row>
+    <row r="373" ht="40" customHeight="1">
+      <c r="A373" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B373" s="12" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C373" s="12" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D373" s="12" t="inlineStr">
+        <is>
+          <t>744516</t>
+        </is>
+      </c>
+      <c r="E373" s="12" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F373" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 136/150/50 µg/24h
+D.màx: 136/150/50 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G373" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H373" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I373" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J373" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K373" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L373" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M373" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65226</t>
+        </is>
+      </c>
+      <c r="N373" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O373" s="12" t="inlineStr"/>
+      <c r="P373" s="12" t="inlineStr">
+        <is>
+          <t>MATMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B374" s="12" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C374" s="12" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D374" s="12" t="inlineStr">
+        <is>
+          <t>751271</t>
+        </is>
+      </c>
+      <c r="E374" s="12" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F374" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 136/150/50 µg/24h
+D.màx: 136/150/50 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G374" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H374" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I374" s="12" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J374" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K374" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L374" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M374" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65236</t>
+        </is>
+      </c>
+      <c r="N374" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O374" s="12" t="inlineStr"/>
+      <c r="P374" s="12" t="inlineStr">
+        <is>
+          <t>MATMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="40" customHeight="1">
+      <c r="A375" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B375" s="12" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C375" s="12" t="inlineStr">
+        <is>
+          <t>MOMETASONA SANDOZ 50 MICROGRAMOS/DOSIS SUSPENSION PARA PULVERIZACION NASAL , 1 envase de 18 g (140 nebulizaciones)</t>
+        </is>
+      </c>
+      <c r="D375" s="12" t="inlineStr">
+        <is>
+          <t>695268</t>
+        </is>
+      </c>
+      <c r="E375" s="12" t="inlineStr">
+        <is>
+          <t>MOMETASONA SANDOZ 50 MICROGRAMOS/DOSIS SUSPENSION PARA PULVERIZACION NASAL , 1 envase de 18 g (140 nebulizaciones)</t>
+        </is>
+      </c>
+      <c r="F375" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 136/150/50 µg/24h
+D.màx: 136/150/50 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G375" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H375" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I375" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J375" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K375" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L375" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M375" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76859</t>
+        </is>
+      </c>
+      <c r="N375" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O375" s="12" t="inlineStr"/>
+      <c r="P375" s="12" t="inlineStr">
+        <is>
+          <t>MATMA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,11 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +149,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7030,3719 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr"/>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr"/>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr"/>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr"/>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O101" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr"/>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>864967</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63011</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O102" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr"/>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>722187</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83247</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O103" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr"/>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr"/>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>664465</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593002</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr"/>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>664467</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593007</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr"/>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>665951</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09594002</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr"/>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>665952</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09594007</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr"/>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>665938</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09586007</t>
+        </is>
+      </c>
+      <c r="N109" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O109" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr"/>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O110" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr"/>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr"/>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M112" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N112" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O112" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr"/>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr"/>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr"/>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr"/>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>706160</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79736</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr"/>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>653830</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67561</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr"/>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N118" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr"/>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr"/>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 44 µg/24h
+D.màx: 44 µg/24h</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr"/>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>769609</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 55 µg/24h
+D.màx: 55 µg/24h</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP1</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr"/>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>768742</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 55 µg/24h
+D.màx: 55 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP</t>
+        </is>
+      </c>
+      <c r="N122" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr"/>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N123" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr"/>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M124" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N124" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O124" s="11" t="inlineStr"/>
+      <c r="P124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr"/>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr"/>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr"/>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>725241</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83987</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr"/>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>672718</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr"/>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr"/>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>668905</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61663</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr"/>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>660910</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62046</t>
+        </is>
+      </c>
+      <c r="N131" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr"/>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>651927</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59254</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr"/>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>885640</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59255</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr"/>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr"/>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr"/>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr"/>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr"/>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>650966</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66670</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr"/>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>650965</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66669</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr"/>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>650967</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66671</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr"/>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>656614</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59036</t>
+        </is>
+      </c>
+      <c r="N141" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr"/>
+      <c r="P141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr"/>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr"/>
+      <c r="P142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr"/>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
+      <c r="P143" s="11" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr"/>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>945436</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L144" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65536</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr"/>
+      <c r="P144" s="11" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr"/>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>652283</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67103</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr"/>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>689729</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60480</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr"/>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>689687</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60482</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10769,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +10945,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +10977,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11033,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P147"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10743,6 +10743,3897 @@
       <c r="O147" s="11" t="inlineStr"/>
       <c r="P147" s="11" t="inlineStr"/>
     </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>689745</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K148" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L148" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M148" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60479</t>
+        </is>
+      </c>
+      <c r="N148" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O148" s="11" t="inlineStr"/>
+      <c r="P148" s="11" t="inlineStr"/>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>689786</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J149" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K149" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60477</t>
+        </is>
+      </c>
+      <c r="N149" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O149" s="11" t="inlineStr"/>
+      <c r="P149" s="11" t="inlineStr"/>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K150" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L150" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M150" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N150" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O150" s="11" t="inlineStr"/>
+      <c r="P150" s="11" t="inlineStr"/>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>689109</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K151" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60527</t>
+        </is>
+      </c>
+      <c r="N151" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O151" s="11" t="inlineStr"/>
+      <c r="P151" s="11" t="inlineStr"/>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>689141</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H152" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K152" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L152" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M152" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60525</t>
+        </is>
+      </c>
+      <c r="N152" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O152" s="11" t="inlineStr"/>
+      <c r="P152" s="11" t="inlineStr"/>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K153" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N153" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O153" s="11" t="inlineStr"/>
+      <c r="P153" s="11" t="inlineStr"/>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J154" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K154" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M154" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N154" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O154" s="11" t="inlineStr"/>
+      <c r="P154" s="11" t="inlineStr"/>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>662361</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K155" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61971</t>
+        </is>
+      </c>
+      <c r="N155" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr"/>
+      <c r="P155" s="11" t="inlineStr"/>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>662353</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA ACCUHALER 500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H156" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K156" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L156" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M156" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61972</t>
+        </is>
+      </c>
+      <c r="N156" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O156" s="11" t="inlineStr"/>
+      <c r="P156" s="11" t="inlineStr"/>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>665562</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J157" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K157" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61788</t>
+        </is>
+      </c>
+      <c r="N157" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O157" s="11" t="inlineStr"/>
+      <c r="P157" s="11" t="inlineStr"/>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA 50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>665570</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>TRIALONA 50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J158" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K158" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L158" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M158" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61787</t>
+        </is>
+      </c>
+      <c r="N158" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O158" s="11" t="inlineStr"/>
+      <c r="P158" s="11" t="inlineStr"/>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 0,25 MG/ ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>726516</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 0,25 MG/ ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H159" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J159" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K159" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=84405</t>
+        </is>
+      </c>
+      <c r="N159" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O159" s="11" t="inlineStr"/>
+      <c r="P159" s="11" t="inlineStr"/>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 1 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>726517</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>FLUTICASONA ALDO-UNION 1 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H160" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K160" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L160" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M160" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=84406</t>
+        </is>
+      </c>
+      <c r="N160" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O160" s="11" t="inlineStr"/>
+      <c r="P160" s="11" t="inlineStr"/>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>ICSORI 125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>705031</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>ICSORI 125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J161" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K161" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79477</t>
+        </is>
+      </c>
+      <c r="N161" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O161" s="11" t="inlineStr"/>
+      <c r="P161" s="11" t="inlineStr"/>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>ICSORI 250 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>705033</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>ICSORI 250 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H162" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J162" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K162" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L162" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M162" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79478</t>
+        </is>
+      </c>
+      <c r="N162" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O162" s="11" t="inlineStr"/>
+      <c r="P162" s="11" t="inlineStr"/>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>744516</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200 µg/24h
+D.màx: 800 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J163" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K163" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L163" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65226</t>
+        </is>
+      </c>
+      <c r="N163" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O163" s="11" t="inlineStr"/>
+      <c r="P163" s="11" t="inlineStr"/>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>751271</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200 µg/24h
+D.màx: 800 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G164" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H164" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J164" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K164" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L164" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M164" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65236</t>
+        </is>
+      </c>
+      <c r="N164" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O164" s="11" t="inlineStr"/>
+      <c r="P164" s="11" t="inlineStr"/>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H165" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J165" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K165" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N165" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O165" s="11" t="inlineStr"/>
+      <c r="P165" s="11" t="inlineStr"/>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>757412</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G166" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H166" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J166" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K166" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L166" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M166" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87927</t>
+        </is>
+      </c>
+      <c r="N166" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O166" s="11" t="inlineStr"/>
+      <c r="P166" s="11" t="inlineStr"/>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO/SALBUTAMOL CIPLA 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>716518</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO/SALBUTAMOL CIPLA 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J167" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K167" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L167" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=82145</t>
+        </is>
+      </c>
+      <c r="N167" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O167" s="11" t="inlineStr"/>
+      <c r="P167" s="11" t="inlineStr"/>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>707896</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H168" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J168" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K168" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L168" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M168" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80248</t>
+        </is>
+      </c>
+      <c r="N168" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O168" s="11" t="inlineStr"/>
+      <c r="P168" s="11" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>707904</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J169" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K169" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L169" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M169" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80249</t>
+        </is>
+      </c>
+      <c r="N169" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O169" s="11" t="inlineStr"/>
+      <c r="P169" s="11" t="inlineStr"/>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G170" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H170" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J170" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K170" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L170" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M170" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N170" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O170" s="11" t="inlineStr"/>
+      <c r="P170" s="11" t="inlineStr"/>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>700543</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J171" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K171" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L171" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M171" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62840</t>
+        </is>
+      </c>
+      <c r="N171" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O171" s="11" t="inlineStr"/>
+      <c r="P171" s="11" t="inlineStr"/>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C172" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H172" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J172" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K172" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L172" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M172" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62841</t>
+        </is>
+      </c>
+      <c r="N172" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O172" s="11" t="inlineStr"/>
+      <c r="P172" s="11" t="inlineStr"/>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>816264</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H173" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J173" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L173" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M173" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63924</t>
+        </is>
+      </c>
+      <c r="N173" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O173" s="11" t="inlineStr"/>
+      <c r="P173" s="11" t="inlineStr"/>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>817684</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H174" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J174" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K174" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L174" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M174" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63925</t>
+        </is>
+      </c>
+      <c r="N174" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O174" s="11" t="inlineStr"/>
+      <c r="P174" s="11" t="inlineStr"/>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>813089</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J175" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K175" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L175" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M175" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63923</t>
+        </is>
+      </c>
+      <c r="N175" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O175" s="11" t="inlineStr"/>
+      <c r="P175" s="11" t="inlineStr"/>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C176" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D176" s="11" t="inlineStr">
+        <is>
+          <t>848671</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G176" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H176" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J176" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K176" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L176" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M176" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62867</t>
+        </is>
+      </c>
+      <c r="N176" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O176" s="11" t="inlineStr"/>
+      <c r="P176" s="11" t="inlineStr"/>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C177" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>700545</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H177" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J177" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K177" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L177" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M177" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62868</t>
+        </is>
+      </c>
+      <c r="N177" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O177" s="11" t="inlineStr"/>
+      <c r="P177" s="11" t="inlineStr"/>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C178" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="inlineStr">
+        <is>
+          <t>700546</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H178" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J178" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K178" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L178" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M178" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62869</t>
+        </is>
+      </c>
+      <c r="N178" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O178" s="11" t="inlineStr"/>
+      <c r="P178" s="11" t="inlineStr"/>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/125 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>909820</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/125 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H179" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J179" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K179" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L179" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M179" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64065</t>
+        </is>
+      </c>
+      <c r="N179" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O179" s="11" t="inlineStr"/>
+      <c r="P179" s="11" t="inlineStr"/>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C180" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/250 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
+        <is>
+          <t>911610</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/250 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H180" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J180" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K180" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L180" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M180" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64066</t>
+        </is>
+      </c>
+      <c r="N180" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O180" s="11" t="inlineStr"/>
+      <c r="P180" s="11" t="inlineStr"/>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/50 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>906842</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO 25 microgramos/50 microgramos/ INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H181" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J181" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K181" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L181" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M181" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64064</t>
+        </is>
+      </c>
+      <c r="N181" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O181" s="11" t="inlineStr"/>
+      <c r="P181" s="11" t="inlineStr"/>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
+        <is>
+          <t>939959</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H182" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J182" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K182" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M182" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62842</t>
+        </is>
+      </c>
+      <c r="N182" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O182" s="11" t="inlineStr"/>
+      <c r="P182" s="11" t="inlineStr"/>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C183" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>940544</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H183" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J183" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K183" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L183" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M183" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62843</t>
+        </is>
+      </c>
+      <c r="N183" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O183" s="11" t="inlineStr"/>
+      <c r="P183" s="11" t="inlineStr"/>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C184" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D184" s="11" t="inlineStr">
+        <is>
+          <t>940551</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H184" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J184" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K184" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L184" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M184" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62844</t>
+        </is>
+      </c>
+      <c r="N184" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O184" s="11" t="inlineStr"/>
+      <c r="P184" s="11" t="inlineStr"/>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C185" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>932228</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H185" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I185" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J185" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K185" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L185" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M185" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63870</t>
+        </is>
+      </c>
+      <c r="N185" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O185" s="11" t="inlineStr"/>
+      <c r="P185" s="11" t="inlineStr"/>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C186" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/250 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D186" s="11" t="inlineStr">
+        <is>
+          <t>932236</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/250 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H186" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J186" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K186" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L186" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M186" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63871</t>
+        </is>
+      </c>
+      <c r="N186" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O186" s="11" t="inlineStr"/>
+      <c r="P186" s="11" t="inlineStr"/>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C187" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/50 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>932178</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/50 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H187" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J187" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K187" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L187" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M187" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63869</t>
+        </is>
+      </c>
+      <c r="N187" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O187" s="11" t="inlineStr"/>
+      <c r="P187" s="11" t="inlineStr"/>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/100 microgramos/inhalación, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D188" s="11" t="inlineStr">
+        <is>
+          <t>804732</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/100 microgramos/inhalación, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H188" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K188" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L188" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M188" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62667</t>
+        </is>
+      </c>
+      <c r="N188" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O188" s="11" t="inlineStr"/>
+      <c r="P188" s="11" t="inlineStr"/>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C189" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>700538</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H189" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I189" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J189" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K189" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L189" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M189" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62668</t>
+        </is>
+      </c>
+      <c r="N189" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O189" s="11" t="inlineStr"/>
+      <c r="P189" s="11" t="inlineStr"/>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C190" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D190" s="11" t="inlineStr">
+        <is>
+          <t>700539</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G190" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H190" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J190" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K190" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L190" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M190" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62669</t>
+        </is>
+      </c>
+      <c r="N190" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O190" s="11" t="inlineStr"/>
+      <c r="P190" s="11" t="inlineStr"/>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C191" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/125 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>874578</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/125 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H191" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K191" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L191" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M191" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63797</t>
+        </is>
+      </c>
+      <c r="N191" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O191" s="11" t="inlineStr"/>
+      <c r="P191" s="11" t="inlineStr"/>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C192" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/250 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D192" s="11" t="inlineStr">
+        <is>
+          <t>874586</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/250 microgramos/INHALACIÓN,  SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H192" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I192" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J192" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K192" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L192" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M192" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63798</t>
+        </is>
+      </c>
+      <c r="N192" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O192" s="11" t="inlineStr"/>
+      <c r="P192" s="11" t="inlineStr"/>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C193" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/50 microgramos/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>874354</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 microgramos/50 microgramos/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H193" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I193" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J193" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K193" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L193" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M193" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63796</t>
+        </is>
+      </c>
+      <c r="N193" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O193" s="11" t="inlineStr"/>
+      <c r="P193" s="11" t="inlineStr"/>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D194" s="11" t="inlineStr">
+        <is>
+          <t>730593</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G194" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H194" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I194" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J194" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K194" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L194" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M194" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85851</t>
+        </is>
+      </c>
+      <c r="N194" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O194" s="11" t="inlineStr"/>
+      <c r="P194" s="11" t="inlineStr"/>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>730594</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H195" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J195" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K195" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L195" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M195" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85852</t>
+        </is>
+      </c>
+      <c r="N195" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O195" s="11" t="inlineStr"/>
+      <c r="P195" s="11" t="inlineStr"/>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D196" s="11" t="inlineStr">
+        <is>
+          <t>730595</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H196" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J196" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K196" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L196" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M196" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85853</t>
+        </is>
+      </c>
+      <c r="N196" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O196" s="11" t="inlineStr"/>
+      <c r="P196" s="11" t="inlineStr"/>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>FLUSAMIX EASYHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>724210</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>FLUSAMIX EASYHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H197" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I197" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J197" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K197" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L197" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M197" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83644</t>
+        </is>
+      </c>
+      <c r="N197" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O197" s="11" t="inlineStr"/>
+      <c r="P197" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10769,7 +14660,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -10945,7 +14835,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -10977,7 +14866,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -11033,7 +14921,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14634,6 +14634,3906 @@
       <c r="O197" s="11" t="inlineStr"/>
       <c r="P197" s="11" t="inlineStr"/>
     </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D198" s="11" t="inlineStr">
+        <is>
+          <t>730581</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H198" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I198" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J198" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K198" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L198" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M198" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85847</t>
+        </is>
+      </c>
+      <c r="N198" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O198" s="11" t="inlineStr"/>
+      <c r="P198" s="11" t="inlineStr"/>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>730585</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>INHALOK AIRMASTER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H199" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J199" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K199" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L199" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M199" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85848</t>
+        </is>
+      </c>
+      <c r="N199" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O199" s="11" t="inlineStr"/>
+      <c r="P199" s="11" t="inlineStr"/>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D200" s="11" t="inlineStr">
+        <is>
+          <t>712329</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G200" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H200" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J200" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K200" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L200" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M200" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81181</t>
+        </is>
+      </c>
+      <c r="N200" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O200" s="11" t="inlineStr"/>
+      <c r="P200" s="11" t="inlineStr"/>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C201" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/250 MICOGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D201" s="11" t="inlineStr">
+        <is>
+          <t>712330</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 25 MICROGRAMOS/250 MICOGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H201" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I201" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J201" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K201" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L201" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M201" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81182</t>
+        </is>
+      </c>
+      <c r="N201" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O201" s="11" t="inlineStr"/>
+      <c r="P201" s="11" t="inlineStr"/>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D202" s="11" t="inlineStr">
+        <is>
+          <t>714997</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G202" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H202" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J202" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K202" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L202" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M202" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81790</t>
+        </is>
+      </c>
+      <c r="N202" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O202" s="11" t="inlineStr"/>
+      <c r="P202" s="11" t="inlineStr"/>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C203" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D203" s="11" t="inlineStr">
+        <is>
+          <t>715006</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>SALMETEROL/FLUTICASONA CIPLA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS) 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H203" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J203" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K203" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L203" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M203" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81791</t>
+        </is>
+      </c>
+      <c r="N203" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O203" s="11" t="inlineStr"/>
+      <c r="P203" s="11" t="inlineStr"/>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12,75 microgramos/100 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D204" s="11" t="inlineStr">
+        <is>
+          <t>730928</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12,75 microgramos/100 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F204" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H204" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I204" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J204" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K204" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L204" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M204" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211533001</t>
+        </is>
+      </c>
+      <c r="N204" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O204" s="11" t="inlineStr"/>
+      <c r="P204" s="11" t="inlineStr"/>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C205" s="11" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12.75 microgramos/202 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D205" s="11" t="inlineStr">
+        <is>
+          <t>730997</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>SEFFALAIR SPIROMAX 12.75 microgramos/202 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H205" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J205" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K205" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L205" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M205" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1211533003</t>
+        </is>
+      </c>
+      <c r="N205" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O205" s="11" t="inlineStr"/>
+      <c r="P205" s="11" t="inlineStr"/>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D206" s="11" t="inlineStr">
+        <is>
+          <t>769894</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H206" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K206" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L206" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M206" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410100C</t>
+        </is>
+      </c>
+      <c r="N206" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O206" s="11" t="inlineStr"/>
+      <c r="P206" s="11" t="inlineStr"/>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C207" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>763682</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/100 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H207" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K207" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L207" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M207" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8324IP</t>
+        </is>
+      </c>
+      <c r="N207" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O207" s="11" t="inlineStr"/>
+      <c r="P207" s="11" t="inlineStr"/>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D208" s="11" t="inlineStr">
+        <is>
+          <t>769911</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G208" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H208" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J208" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K208" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L208" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M208" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=122901</t>
+        </is>
+      </c>
+      <c r="N208" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O208" s="11" t="inlineStr"/>
+      <c r="P208" s="11" t="inlineStr"/>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>769013</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H209" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J209" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K209" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L209" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M209" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410200C</t>
+        </is>
+      </c>
+      <c r="N209" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O209" s="11" t="inlineStr"/>
+      <c r="P209" s="11" t="inlineStr"/>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D210" s="11" t="inlineStr">
+        <is>
+          <t>763694</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/250 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN., 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H210" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J210" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K210" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L210" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M210" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8325IP</t>
+        </is>
+      </c>
+      <c r="N210" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O210" s="11" t="inlineStr"/>
+      <c r="P210" s="11" t="inlineStr"/>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>769014</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H211" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J211" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K211" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L211" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M211" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1410300C</t>
+        </is>
+      </c>
+      <c r="N211" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O211" s="11" t="inlineStr"/>
+      <c r="P211" s="11" t="inlineStr"/>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>763712</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE ACCUHALER 50 MICROGRAMOS/500 MICROGRAMOS/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H212" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J212" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K212" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L212" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M212" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=8326IP</t>
+        </is>
+      </c>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O212" s="11" t="inlineStr"/>
+      <c r="P212" s="11" t="inlineStr"/>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION,  SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>769640</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION,  SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J213" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K213" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L213" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M213" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=506780100</t>
+        </is>
+      </c>
+      <c r="N213" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O213" s="11" t="inlineStr"/>
+      <c r="P213" s="11" t="inlineStr"/>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D214" s="11" t="inlineStr">
+        <is>
+          <t>763309</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/125 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H214" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I214" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J214" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K214" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L214" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M214" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=9070IP</t>
+        </is>
+      </c>
+      <c r="N214" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O214" s="11" t="inlineStr"/>
+      <c r="P214" s="11" t="inlineStr"/>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C215" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D215" s="11" t="inlineStr">
+        <is>
+          <t>763551</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>SERETIDE 25 MICROGRAMOS/50 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H215" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J215" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K215" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L215" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M215" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=9069IP</t>
+        </is>
+      </c>
+      <c r="N215" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O215" s="11" t="inlineStr"/>
+      <c r="P215" s="11" t="inlineStr"/>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="D216" s="11" t="inlineStr">
+        <is>
+          <t>723302</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G216" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H216" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I216" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J216" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K216" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L216" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M216" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78813</t>
+        </is>
+      </c>
+      <c r="N216" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O216" s="11" t="inlineStr"/>
+      <c r="P216" s="11" t="inlineStr"/>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B217" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C217" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="D217" s="11" t="inlineStr">
+        <is>
+          <t>723299</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H217" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I217" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J217" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K217" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L217" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M217" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78803</t>
+        </is>
+      </c>
+      <c r="N217" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O217" s="11" t="inlineStr"/>
+      <c r="P217" s="11" t="inlineStr"/>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>RILAST FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D218" s="11" t="inlineStr">
+        <is>
+          <t>723312</t>
+        </is>
+      </c>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>RILAST FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G218" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H218" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I218" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J218" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K218" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L218" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M218" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65045</t>
+        </is>
+      </c>
+      <c r="N218" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O218" s="11" t="inlineStr"/>
+      <c r="P218" s="11" t="inlineStr"/>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B219" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D219" s="11" t="inlineStr">
+        <is>
+          <t>723315</t>
+        </is>
+      </c>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H219" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J219" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K219" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L219" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M219" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64353</t>
+        </is>
+      </c>
+      <c r="N219" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O219" s="11" t="inlineStr"/>
+      <c r="P219" s="11" t="inlineStr"/>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D220" s="11" t="inlineStr">
+        <is>
+          <t>723306</t>
+        </is>
+      </c>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>RILAST TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G220" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H220" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J220" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K220" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L220" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M220" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=64354</t>
+        </is>
+      </c>
+      <c r="N220" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O220" s="11" t="inlineStr"/>
+      <c r="P220" s="11" t="inlineStr"/>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B221" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C221" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D221" s="11" t="inlineStr">
+        <is>
+          <t>723313</t>
+        </is>
+      </c>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT FORTE TURBUHALER 320 microgramos/9 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H221" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I221" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J221" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K221" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L221" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M221" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65044</t>
+        </is>
+      </c>
+      <c r="N221" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O221" s="11" t="inlineStr"/>
+      <c r="P221" s="11" t="inlineStr"/>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D222" s="11" t="inlineStr">
+        <is>
+          <t>723314</t>
+        </is>
+      </c>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 160 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G222" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H222" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I222" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J222" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K222" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L222" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M222" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63958</t>
+        </is>
+      </c>
+      <c r="N222" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O222" s="11" t="inlineStr"/>
+      <c r="P222" s="11" t="inlineStr"/>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C223" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D223" s="11" t="inlineStr">
+        <is>
+          <t>723311</t>
+        </is>
+      </c>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT TURBUHALER 80 microgramos/4,5 microgramos/INHALACION  POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G223" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H223" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I223" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J223" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K223" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L223" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M223" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63956</t>
+        </is>
+      </c>
+      <c r="N223" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O223" s="11" t="inlineStr"/>
+      <c r="P223" s="11" t="inlineStr"/>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B224" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D224" s="11" t="inlineStr">
+        <is>
+          <t>723307</t>
+        </is>
+      </c>
+      <c r="E224" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F224" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G224" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H224" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I224" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J224" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K224" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L224" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M224" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81115</t>
+        </is>
+      </c>
+      <c r="N224" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O224" s="11" t="inlineStr"/>
+      <c r="P224" s="11" t="inlineStr"/>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B225" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT 80 MICROGRAMOS/2,25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D225" s="11" t="inlineStr">
+        <is>
+          <t>728894</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>SYMBICORT 80 MICROGRAMOS/2,25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F225" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G225" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H225" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J225" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K225" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L225" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M225" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85232</t>
+        </is>
+      </c>
+      <c r="N225" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O225" s="11" t="inlineStr"/>
+      <c r="P225" s="11" t="inlineStr"/>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 160 microgramos / 4,5 microgramos polvo para inhalacion 120 dosis</t>
+        </is>
+      </c>
+      <c r="D226" s="11" t="inlineStr">
+        <is>
+          <t>723304</t>
+        </is>
+      </c>
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 160 microgramos / 4,5 microgramos polvo para inhalacion 120 dosis</t>
+        </is>
+      </c>
+      <c r="F226" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G226" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H226" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I226" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J226" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K226" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L226" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M226" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114921001</t>
+        </is>
+      </c>
+      <c r="N226" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O226" s="11" t="inlineStr"/>
+      <c r="P226" s="11" t="inlineStr"/>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C227" s="11" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 320 microgramos / 9 microgramos polvo para inhalacion 60 dosis</t>
+        </is>
+      </c>
+      <c r="D227" s="11" t="inlineStr">
+        <is>
+          <t>723305</t>
+        </is>
+      </c>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>BiResp Spiromax 320 microgramos / 9 microgramos polvo para inhalacion 60 dosis</t>
+        </is>
+      </c>
+      <c r="F227" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H227" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J227" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K227" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L227" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M227" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114921004</t>
+        </is>
+      </c>
+      <c r="N227" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O227" s="11" t="inlineStr"/>
+      <c r="P227" s="11" t="inlineStr"/>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D228" s="11" t="inlineStr">
+        <is>
+          <t>723825</t>
+        </is>
+      </c>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F228" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G228" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H228" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J228" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K228" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L228" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M228" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N228" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O228" s="11" t="inlineStr"/>
+      <c r="P228" s="11" t="inlineStr"/>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B229" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C229" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="D229" s="11" t="inlineStr">
+        <is>
+          <t>731458</t>
+        </is>
+      </c>
+      <c r="E229" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="F229" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G229" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H229" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I229" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J229" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K229" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L229" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M229" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N229" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O229" s="11" t="inlineStr"/>
+      <c r="P229" s="11" t="inlineStr"/>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D230" s="11" t="inlineStr">
+        <is>
+          <t>730557</t>
+        </is>
+      </c>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F230" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G230" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H230" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I230" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J230" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K230" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L230" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M230" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85833</t>
+        </is>
+      </c>
+      <c r="N230" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O230" s="11" t="inlineStr"/>
+      <c r="P230" s="11" t="inlineStr"/>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B231" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C231" s="11" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 160 MICROGRAMOS/4.5 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 120 dosis</t>
+        </is>
+      </c>
+      <c r="D231" s="11" t="inlineStr">
+        <is>
+          <t>723300</t>
+        </is>
+      </c>
+      <c r="E231" s="11" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 160 MICROGRAMOS/4.5 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 120 dosis</t>
+        </is>
+      </c>
+      <c r="F231" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G231" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H231" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I231" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J231" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K231" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L231" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M231" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78807</t>
+        </is>
+      </c>
+      <c r="N231" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O231" s="11" t="inlineStr"/>
+      <c r="P231" s="11" t="inlineStr"/>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 320 MICROGRAMOS//9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="D232" s="11" t="inlineStr">
+        <is>
+          <t>723301</t>
+        </is>
+      </c>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>BUFOMIX EASYHALER 320 MICROGRAMOS//9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="F232" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G232" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H232" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I232" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J232" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K232" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L232" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M232" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78808</t>
+        </is>
+      </c>
+      <c r="N232" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O232" s="11" t="inlineStr"/>
+      <c r="P232" s="11" t="inlineStr"/>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C233" s="11" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 160 microgramos/4,5 microgramos polvo para inhalacion 1 inhalador con 120 dosis</t>
+        </is>
+      </c>
+      <c r="D233" s="11" t="inlineStr">
+        <is>
+          <t>723297</t>
+        </is>
+      </c>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 160 microgramos/4,5 microgramos polvo para inhalacion 1 inhalador con 120 dosis</t>
+        </is>
+      </c>
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G233" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H233" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J233" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K233" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L233" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M233" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114920001</t>
+        </is>
+      </c>
+      <c r="N233" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O233" s="11" t="inlineStr"/>
+      <c r="P233" s="11" t="inlineStr"/>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 320 microgramos/9 microgramos polvo para inhalacion 1 inhalador con 60 dosis</t>
+        </is>
+      </c>
+      <c r="D234" s="11" t="inlineStr">
+        <is>
+          <t>723298</t>
+        </is>
+      </c>
+      <c r="E234" s="11" t="inlineStr">
+        <is>
+          <t>DuoResp Spiromax 320 microgramos/9 microgramos polvo para inhalacion 1 inhalador con 60 dosis</t>
+        </is>
+      </c>
+      <c r="F234" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G234" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H234" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I234" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J234" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K234" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11892</t>
+        </is>
+      </c>
+      <c r="L234" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M234" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114920004</t>
+        </is>
+      </c>
+      <c r="N234" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O234" s="11" t="inlineStr"/>
+      <c r="P234" s="11" t="inlineStr"/>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C235" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F235" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G235" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H235" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I235" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J235" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K235" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L235" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M235" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N235" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O235" s="11" t="inlineStr"/>
+      <c r="P235" s="11" t="inlineStr"/>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D236" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F236" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H236" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I236" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J236" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K236" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L236" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M236" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N236" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O236" s="11" t="inlineStr"/>
+      <c r="P236" s="11" t="inlineStr"/>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B237" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C237" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D237" s="11" t="inlineStr">
+        <is>
+          <t>700582</t>
+        </is>
+      </c>
+      <c r="E237" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F237" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H237" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I237" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J237" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K237" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L237" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M237" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76740</t>
+        </is>
+      </c>
+      <c r="N237" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O237" s="11" t="inlineStr"/>
+      <c r="P237" s="11" t="inlineStr"/>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D238" s="11" t="inlineStr">
+        <is>
+          <t>710249</t>
+        </is>
+      </c>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F238" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G238" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H238" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I238" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J238" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K238" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L238" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M238" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80708</t>
+        </is>
+      </c>
+      <c r="N238" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O238" s="11" t="inlineStr"/>
+      <c r="P238" s="11" t="inlineStr"/>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C239" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>659075</t>
+        </is>
+      </c>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F239" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G239" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H239" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I239" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J239" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K239" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L239" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M239" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68809</t>
+        </is>
+      </c>
+      <c r="N239" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O239" s="11" t="inlineStr"/>
+      <c r="P239" s="11" t="inlineStr"/>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B240" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D240" s="11" t="inlineStr">
+        <is>
+          <t>709802</t>
+        </is>
+      </c>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F240" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G240" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H240" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I240" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J240" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K240" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L240" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M240" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80600</t>
+        </is>
+      </c>
+      <c r="N240" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O240" s="11" t="inlineStr"/>
+      <c r="P240" s="11" t="inlineStr"/>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B241" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C241" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D241" s="11" t="inlineStr">
+        <is>
+          <t>700581</t>
+        </is>
+      </c>
+      <c r="E241" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F241" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G241" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H241" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I241" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J241" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K241" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L241" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M241" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76713</t>
+        </is>
+      </c>
+      <c r="N241" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O241" s="11" t="inlineStr"/>
+      <c r="P241" s="11" t="inlineStr"/>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="D242" s="11" t="inlineStr">
+        <is>
+          <t>710247</t>
+        </is>
+      </c>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="F242" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G242" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H242" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I242" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J242" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K242" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L242" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M242" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80707</t>
+        </is>
+      </c>
+      <c r="N242" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O242" s="11" t="inlineStr"/>
+      <c r="P242" s="11" t="inlineStr"/>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B243" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C243" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D243" s="11" t="inlineStr">
+        <is>
+          <t>659065</t>
+        </is>
+      </c>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F243" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G243" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H243" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I243" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J243" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K243" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L243" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M243" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68802</t>
+        </is>
+      </c>
+      <c r="N243" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O243" s="11" t="inlineStr"/>
+      <c r="P243" s="11" t="inlineStr"/>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D244" s="11" t="inlineStr">
+        <is>
+          <t>709801</t>
+        </is>
+      </c>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F244" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G244" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H244" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I244" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J244" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K244" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L244" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M244" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80599</t>
+        </is>
+      </c>
+      <c r="N244" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O244" s="11" t="inlineStr"/>
+      <c r="P244" s="11" t="inlineStr"/>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="inlineStr">
+        <is>
+          <t>LUFORBEC 100 MICROGRAMOS/6 MICROGRAMOS/PULSACIÓN SOLUCIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D245" s="11" t="inlineStr">
+        <is>
+          <t>761741</t>
+        </is>
+      </c>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>LUFORBEC 100 MICROGRAMOS/6 MICROGRAMOS/PULSACIÓN SOLUCIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F245" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G245" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H245" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J245" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K245" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L245" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M245" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=88525</t>
+        </is>
+      </c>
+      <c r="N245" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O245" s="11" t="inlineStr"/>
+      <c r="P245" s="11" t="inlineStr"/>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + vilanterol</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 184 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D246" s="11" t="inlineStr">
+        <is>
+          <t>700812</t>
+        </is>
+      </c>
+      <c r="E246" s="11" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 184 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F246" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 22/92 µg/24h
+D.màx: 22/184 µg/24h
+Asma baixa: 22/92 µg/24h
+Asma mitjana: 22/92 µg/24h
+Asma alta: 22/184 µg/24h</t>
+        </is>
+      </c>
+      <c r="G246" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H246" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I246" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J246" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K246" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L246" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M246" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113886005</t>
+        </is>
+      </c>
+      <c r="N246" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O246" s="11" t="inlineStr"/>
+      <c r="P246" s="11" t="inlineStr"/>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B247" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + vilanterol</t>
+        </is>
+      </c>
+      <c r="C247" s="11" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="D247" s="11" t="inlineStr">
+        <is>
+          <t>700811</t>
+        </is>
+      </c>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>RELVAR ELLIPTA 92 MCG/22 MCG POLVO PARA INHALACION (UNIDODIS), 30 dosis</t>
+        </is>
+      </c>
+      <c r="F247" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 22/92 µg/24h
+D.màx: 22/184 µg/24h
+Asma baixa: 22/92 µg/24h
+Asma mitjana: 22/92 µg/24h
+Asma alta: 22/184 µg/24h</t>
+        </is>
+      </c>
+      <c r="G247" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H247" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I247" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J247" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K247" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L247" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M247" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=113886002</t>
+        </is>
+      </c>
+      <c r="N247" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O247" s="11" t="inlineStr"/>
+      <c r="P247" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3918 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O101" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>864967</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL CLICKHALER POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63011</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>salmeterol</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>722187</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>SOLTEL 25 MICROGRAMOS/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 50 µg/12h
+D.màx: 100 µg/12h</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83247</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L104" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M104" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N104" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>664465</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 150 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K105" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L105" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M105" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593002</t>
+        </is>
+      </c>
+      <c r="N105" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>664467</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>ONBREZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M106" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09593007</t>
+        </is>
+      </c>
+      <c r="N106" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>665952</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>HIROBRIZ BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L107" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09594007</t>
+        </is>
+      </c>
+      <c r="N107" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P107" s="12" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>indacaterol</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>665938</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>OSLIF BREEZHALER 300 microgramos POLVO PARA INHALACION (CAPSULA DURA), 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 150 µg/24h
+D.màx: 300 µg/24h</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L108" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=09586007</t>
+        </is>
+      </c>
+      <c r="N108" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M112" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N112" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>706160</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>IPRATROPIO BROMURO CIPLA 20 MICROGRAMOS SOLUCION PARA INHALACION EN ENVASE A PRESION , 200 dosis</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79736</t>
+        </is>
+      </c>
+      <c r="N115" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P115" s="12" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>653830</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 250 microgramos/ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 1 ml</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67561</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K117" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N117" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N118" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>glicopirronio</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 44 µg/24h
+D.màx: 44 µg/24h</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L119" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N119" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="12" t="inlineStr"/>
+      <c r="P119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>bromuro umeclidinio</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>769609</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 MCG POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 55 µg/24h
+D.màx: 55 µg/24h</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K120" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L120" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M120" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP1</t>
+        </is>
+      </c>
+      <c r="N120" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="12" t="inlineStr"/>
+      <c r="P120" s="12" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>bromuro umeclidinio</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>768742</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>INCRUSE ELLIPTA 55 mcg POLVO PARA INHALACION UNIDOSIS, 30 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 55 µg/24h
+D.màx: 55 µg/24h</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K121" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11818</t>
+        </is>
+      </c>
+      <c r="L121" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114922002IP</t>
+        </is>
+      </c>
+      <c r="N121" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="12" t="inlineStr"/>
+      <c r="P121" s="12" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O122" s="12" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O123" s="12" t="inlineStr"/>
+      <c r="P123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M124" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N124" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="11" t="inlineStr"/>
+      <c r="P124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>725241</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83987</t>
+        </is>
+      </c>
+      <c r="N126" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="12" t="inlineStr"/>
+      <c r="P126" s="12" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>672718</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L127" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N127" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="12" t="inlineStr"/>
+      <c r="P127" s="12" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N128" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="12" t="inlineStr"/>
+      <c r="P128" s="12" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>668905</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61663</t>
+        </is>
+      </c>
+      <c r="N129" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="12" t="inlineStr"/>
+      <c r="P129" s="12" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>660910</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 100 microgramos/inhalacion POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62046</t>
+        </is>
+      </c>
+      <c r="N130" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="12" t="inlineStr"/>
+      <c r="P130" s="12" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>651927</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 200 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59254</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O131" s="12" t="inlineStr"/>
+      <c r="P131" s="12" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>885640</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT TURBUHALER 400 microgramos/inhalación POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L132" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59255</t>
+        </is>
+      </c>
+      <c r="N132" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="12" t="inlineStr"/>
+      <c r="P132" s="12" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>650966</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 100 microgramos POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66670</t>
+        </is>
+      </c>
+      <c r="N137" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="12" t="inlineStr"/>
+      <c r="P137" s="12" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>650965</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 200 mcg POLVO PARA INHALACION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L138" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66669</t>
+        </is>
+      </c>
+      <c r="N138" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="12" t="inlineStr"/>
+      <c r="P138" s="12" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>650967</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA EASYHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66671</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="12" t="inlineStr"/>
+      <c r="P139" s="12" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>656614</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN INFANTIL 50 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59036</t>
+        </is>
+      </c>
+      <c r="N140" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="12" t="inlineStr"/>
+      <c r="P140" s="12" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O141" s="12" t="inlineStr"/>
+      <c r="P141" s="12" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O142" s="12" t="inlineStr"/>
+      <c r="P142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>945436</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 200 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65536</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O143" s="12" t="inlineStr"/>
+      <c r="P143" s="12" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>652283</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>NOVOPULM NOVOLIZER 400 microgramos POLVO PARA INHALACION , 1 inhalador + 1 cartucho de 100 dosis</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11882</t>
+        </is>
+      </c>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=67103</t>
+        </is>
+      </c>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O144" s="12" t="inlineStr"/>
+      <c r="P144" s="12" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>689729</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K145" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60480</t>
+        </is>
+      </c>
+      <c r="N145" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="12" t="inlineStr"/>
+      <c r="P145" s="12" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>689687</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K146" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L146" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M146" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60482</t>
+        </is>
+      </c>
+      <c r="N146" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="12" t="inlineStr"/>
+      <c r="P146" s="12" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>689745</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I147" s="12" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K147" s="12" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60479</t>
+        </is>
+      </c>
+      <c r="N147" s="12" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="12" t="inlineStr"/>
+      <c r="P147" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10976,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +11152,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +11184,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11240,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3478 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>707896</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr"/>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80248</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>707904</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr"/>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80249</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr"/>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr"/>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>700543</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr"/>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62840</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O101" s="11" t="inlineStr"/>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr"/>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62841</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O102" s="11" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>816264</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr"/>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63924</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O103" s="11" t="inlineStr"/>
+      <c r="P103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>817684</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr"/>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63925</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>813089</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr"/>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63923</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>744516</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr"/>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65226</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>751271</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr"/>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65236</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr"/>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr"/>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr"/>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="12" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr"/>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" s="12" t="inlineStr"/>
+      <c r="L111" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M111" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N111" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O111" s="12" t="inlineStr"/>
+      <c r="P111" s="12" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr"/>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="12" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr"/>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr"/>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr"/>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr"/>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr"/>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr"/>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="inlineStr"/>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N118" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O118" s="12" t="inlineStr"/>
+      <c r="P118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr"/>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="inlineStr"/>
+      <c r="L119" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N119" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O119" s="12" t="inlineStr"/>
+      <c r="P119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>725241</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr"/>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83987</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>672718</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr"/>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr"/>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N122" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>668905</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr"/>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61663</t>
+        </is>
+      </c>
+      <c r="N123" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr"/>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr"/>
+      <c r="P124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>roflumilast</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>DAXAS 250 MICROGRAMOS COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>724559</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>DAXAS 250 MICROGRAMOS COMPRIMIDOS, 28 comprimidos</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr"/>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=110636008</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>roflumilast</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>DAXAS 500 MICROGRAMOS COMPRIMIDOS RECUBIERTOS CON PELICULA, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>665845</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>DAXAS 500 MICROGRAMOS COMPRIMIDOS RECUBIERTOS CON PELICULA, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr"/>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=10636002</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>emtricitabina + tenofovir</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>EMTRICITABINA/TENOFOVIR DISOPROXILO GLENMARK 200 MG/245 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>716846</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>EMTRICITABINA/TENOFOVIR DISOPROXILO GLENMARK 200 MG/245 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG, 30 comprimidos</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr"/>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=82260</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>benralizumab</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>FASENRA 30 MG SOLUCION INYECTABLE EN JERINGA PRECARGADA, 1 jeringa precargada de 1 ml</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>720415</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>FASENRA 30 MG SOLUCION INYECTABLE EN JERINGA PRECARGADA, 1 jeringa precargada de 1 ml</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr"/>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1171252001</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>benralizumab</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>FASENRA 30 MG SOLUCION INYECTABLE EN PLUMA PRECARGADA, 1 pluma precargada de 1 ml</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>726705</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>FASENRA 30 MG SOLUCION INYECTABLE EN PLUMA PRECARGADA, 1 pluma precargada de 1 ml</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr"/>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1171252002</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>689729</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr"/>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60480</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>689687</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr"/>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60482</t>
+        </is>
+      </c>
+      <c r="N131" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>689745</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr"/>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60479</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>689786</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr"/>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60477</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr"/>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>689109</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr"/>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60527</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>689141</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr"/>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60525</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr"/>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr"/>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr"/>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>700582</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr"/>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76740</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>710249</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr"/>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80708</t>
+        </is>
+      </c>
+      <c r="N141" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr"/>
+      <c r="P141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>659075</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr"/>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68809</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr"/>
+      <c r="P142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>709802</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr"/>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80600</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
+      <c r="P143" s="11" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>700581</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr"/>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L144" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76713</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr"/>
+      <c r="P144" s="11" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>710247</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr"/>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80707</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>659065</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr"/>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68802</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>PENDENT</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>709801</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr"/>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80599</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10536,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +10712,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +10744,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +10800,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3871 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>707896</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80248</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>707904</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>AIRFLUSAL FORSPIRO 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS) , 1 x 60 dosis</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11819</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80249</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr"/>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>700543</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/250 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62840</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O101" s="11" t="inlineStr"/>
+      <c r="P101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62841</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O102" s="11" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>816264</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/125 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63924</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O103" s="11" t="inlineStr"/>
+      <c r="P103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>817684</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63925</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>813089</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA 25 MICROGRAMOS/50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63923</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>744516</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 200 microgramos POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200 µg/24h
+D.màx: 800 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65226</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>mometasona</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>751271</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>ASMANEX TWISTHALER 400 microgramos POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200 µg/24h
+D.màx: 800 µg/24h
+Asma baixa: 200 µg/24h
+Asma mitjana: 400 µg/24h
+Asma alta: 800 µg/24h</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11894</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65236</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" s="12" t="inlineStr"/>
+      <c r="L111" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M111" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N111" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O111" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P111" s="12" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="inlineStr"/>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N118" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O118" s="12" t="inlineStr"/>
+      <c r="P118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="inlineStr"/>
+      <c r="L119" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N119" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O119" s="12" t="inlineStr"/>
+      <c r="P119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>725241</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 100 MICROGRAMOS/PULSACION SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83987</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>672718</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N122" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>668905</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA  ALDO-UNION 50 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN , 1 envase aerosol de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61663</t>
+        </is>
+      </c>
+      <c r="N123" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr"/>
+      <c r="P124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>689729</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60480</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>689687</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60482</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>689745</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 250 MICROGRAMOS/INHALACIÓN, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60479</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>689786</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 50 MICROGRAMOS/INHALACION, SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60477</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>689109</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 250 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60527</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>689141</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL 50 MICROGRAMOS/INHALACION, SUSPENSION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60525</t>
+        </is>
+      </c>
+      <c r="N131" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>700582</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76740</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>710249</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80708</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>659075</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68809</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>709802</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>FORMODUAL 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 envase de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80600</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>700581</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 100 MICROGRAMOS/6 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=76713</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>710247</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER NEXTHALER 200 MICROGRAMOS/6 MICROGRAMOS POR INHALACION POLVO PARA INHALACION , 1 inhalador de 120 pulsaciones ( PET/Al/PE)</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11881</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80707</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>659065</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 100 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=68802</t>
+        </is>
+      </c>
+      <c r="N141" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O141" s="11" t="inlineStr"/>
+      <c r="P141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>709801</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>FOSTER 200 MICROGRAMOS /6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=80599</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr"/>
+      <c r="P142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>723302</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION ,120 dosis</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78813</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="inlineStr"/>
+      <c r="P143" s="11" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>723299</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>GIBITER EASYHALER 320 MICROGRAMOS/9 MICROGRAMOS/INHALACION POLVO PARA INHALACION , 60 dosis</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11817</t>
+        </is>
+      </c>
+      <c r="L144" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78803</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr"/>
+      <c r="P144" s="11" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>848671</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>INALADUO ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62867</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10929,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +11105,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +11137,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11193,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3822 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr"/>
+      <c r="L101" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr"/>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr"/>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="12" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="12" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N118" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="11" t="inlineStr"/>
+      <c r="P118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>940551</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62844</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>932228</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63870</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="inlineStr"/>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O122" s="12" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr"/>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O123" s="12" t="inlineStr"/>
+      <c r="P123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="inlineStr"/>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N125" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P125" s="12" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>glicopirronio</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 44 µg/24h
+D.màx: 44 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>726795</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79967</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr"/>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>726790</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79966</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>730593</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85851</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>730594</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85852</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>730595</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85853</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>728970</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439006</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>728971</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439010</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>728969</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439002</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr"/>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P141" s="12" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>757412</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr"/>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87927</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O142" s="12" t="inlineStr"/>
+      <c r="P142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr"/>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O143" s="12" t="inlineStr"/>
+      <c r="P143" s="12" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr"/>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O144" s="12" t="inlineStr"/>
+      <c r="P144" s="12" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>723825</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>731458</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10880,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +11056,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +11088,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11144,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3822 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr"/>
+      <c r="L101" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr"/>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr"/>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="12" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="12" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N118" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="11" t="inlineStr"/>
+      <c r="P118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>940551</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62844</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>932228</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63870</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="inlineStr"/>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O122" s="12" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr"/>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O123" s="12" t="inlineStr"/>
+      <c r="P123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="inlineStr"/>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N125" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P125" s="12" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>glicopirronio</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 44 µg/24h
+D.màx: 44 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>726795</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79967</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr"/>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>726790</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79966</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>730593</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85851</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>730594</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85852</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>730595</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85853</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>728970</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439006</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>728971</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439010</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>728969</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439002</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr"/>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P141" s="12" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>757412</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr"/>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87927</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O142" s="12" t="inlineStr"/>
+      <c r="P142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr"/>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O143" s="12" t="inlineStr"/>
+      <c r="P143" s="12" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr"/>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O144" s="12" t="inlineStr"/>
+      <c r="P144" s="12" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>723825</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>731458</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10880,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +11056,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +11088,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11144,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inhaladors MPOC ASMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Llegenda i instruccions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inhaladors MPOC ASMA'!$A$1:$P$97</definedName>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,16 @@
         <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +154,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7038,3822 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>842898</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>ANASMA ACCUHALER 50 microgramos/100 microgramos/INHALACIÓN, POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62839</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>605412</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>ATROALDO 20 microgramos/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=72581</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O99" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>648956</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>678078</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 250 mcg / 2ml SOLUCION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr"/>
+      <c r="L101" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61185</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>648964</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 100 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr"/>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>678086</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>ATROVENT MONODOSIS 500 mcg/ 2ml SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr"/>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61184</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>729878</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441006</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>729879</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441010</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>729877</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>BEMRIST BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas+ 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201441002</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>764529</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 100 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89439</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>764531</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>BIBECFO 200 MICROGRAMOS/6 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 120 pulsaciones</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12/200 µg/12h
+D.màx: 12/400 µg/12h
+Asma baixa: 6/100: 1 inh/12h
+Asma mitjana: 6/100: 2 inh/12h
+Asma alta: 6/200: 2 inh/12h</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=89440</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>651628</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,25 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66943</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O109" s="12" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>651626</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 0,5 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR , 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=66942</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O110" s="12" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>799015</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA ALDO-UNION 200 microgramos/pulsación SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61664</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>677602</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>COMBIPRASAL 0.5 mg/2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73561</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O112" s="12" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>689042</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>FLUSONAL ACCUHALER 500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60530</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>701717</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 125 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUPSENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78536</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>701718</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 250 MICROGRAMOS / 10 MICROGRAMOS/ INHALACION  SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador ( 120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78537</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona + formoterol</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>701719</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>FLUTIFORM 50 MICROGRAMOS / 5 MICROGRAMOS/ INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador (120 pulsaciones)</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/125 µg/12h
+D.màx: 5/250 µg/12h
+Asma baixa: 5/100 µg/12h
+Asma mitjana: 5/250 µg/12h
+Asma alta: 5/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=78538</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>686097</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR ACCUHALER 500 MICROGRAMOS/INHALACIÓN POLVO PARA INHALACIÓN, 1 inhalador + 60 alveolos</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60691</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>fluticasona</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>686154</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>INALACOR 250 MICROGRAMOS/INHALACIÓN SUSPENSIÓN PARA INHALACIÓN EN ENVASE A PRESIÓN, 1 inhalador + 1 cartucho de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 500 µg/12h
+Asma baixa: 100-250 µg/24h
+Asma mitjana: 251-500 µg/24h
+Asma alta: 501-1.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=60688</t>
+        </is>
+      </c>
+      <c r="N118" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O118" s="11" t="inlineStr"/>
+      <c r="P118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>formoterol</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>668871</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>OXIS TURBUHALER  4,5 microgramos/INHALACION POLVO PARA INHALACION , 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 12 µg/12h
+D.màx: 24 µg/12h</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>50-60 l/m</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11893</t>
+        </is>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=61666</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O119" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>940551</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT ACCUHALER 50 microgramos/500 microgramos/INHALACIÓN,  POLVO PARA INHALACIÓN, 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11813</t>
+        </is>
+      </c>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=62844</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>932228</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>PLUSVENT 25 microgramos/125 microgramos/inhalación, suspensión para inhalación envase a presión, 1 inhalador de 120 dosis</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=63870</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>901199</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,25 mg/ml SUSPENSION PARA INHALACION POR  NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="inlineStr"/>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59298</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O122" s="12" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>901082</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>PULMICORT 0,50 mg/ml SUSPENSION PARA INHALACION POR NEBULIZADOR, 5 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr"/>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59297</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O123" s="12" t="inlineStr"/>
+      <c r="P123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>677362</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 2.5 mg SOLUCION PARA INHALACION POR NEBULIZADOR , 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73563</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>677363</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>SALBUAIR 5 mg SOLUCION PARA INHALACION POR NEBULIZADOR, 60 ampollas de 2,5 ml</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="inlineStr"/>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=73562</t>
+        </is>
+      </c>
+      <c r="N125" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P125" s="12" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>607323</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>SALBUTAMOL ALDO-UNION 100 microgramos/dosis SUSPENSION PARA INHALACION EN ENVASE A PRESION  20 inhaladores de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=65850</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O126" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>glicopirronio</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>694302</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>SEEBRI BREEZHALER 44 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA) , 1 inhalador + 30 cápsulas</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 44 µg/24h
+D.màx: 44 µg/24h</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=12778003</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>726795</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT 2,5 MICROGRAMOS/2,5 MICROGRAMOS SOLUCION PARA INHALACION 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79967</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>725702</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>SPIRIVA RESPIMAT 2,5 microgramos SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis)</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=69589</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O129" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>tiotropio</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>731040</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>TAVULUS 18 MICROGRAMOS POLVO PARA INHALACION (CAPSULA DURA), 30 cápsulas + inhalador</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 18 µg/24h (Handihaler) / 5 µg/24h (Respimat) / 10 µg/24h (Zonda)
+D.màx: = pauta</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L130" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85978</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>SABA</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>941807</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>VENTOLIN 5 mg/ml SOLUCION PARA INHALACION POR NEBULIZADOR, 1 frasco de 10 ml</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200 µg si cal
+D.màx: 200 µg/6h</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr"/>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=55147</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>olodaterol + tiotropio</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>726790</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>YANIMO RESPIMAT 2,5 MICROGRAMOS / 2,5 MICROGRAMOS SOLUCION PARA INHALACION, 1 inhalador recargable + 1 cartucho de 60 pulsaciones (30 dosis</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 5/5 µg/24h
+D.màx: 5/5 µg/24h</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11891</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=79966</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>730593</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/100 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85851</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>730594</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/250 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 Inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85852</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>salmeterol + fluticasona</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>730595</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>AMAIRA 50 MICROGRAMOS/500 MICROGRAMOS/INHALACION, POLVO PARA INHALACION (UNIDOSIS), 1 inhalador de 60 dosis</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 50/500 µg/12h
+D.màx: 50/500 µg/12h
+Asma baixa: 50/100 µg/12h
+Asma mitjana: 50/250 µg/12h
+Asma alta: 50/500 µg/12h</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85853</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>728970</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/127,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439006</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>728971</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/260 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439010</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>indacaterol + mometasona</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>728969</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>ATECTURA BREEZHALER 125 microgramos/62,5 microgramos POLVO PARA INHALACION (CAPSULA DURA), 30 x 1 cápsulas (dosis unitaria) + 1 inhalador</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 150/160 µg/24h
+D.màx: 150/160 µg/24h</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>&gt;90 l/m</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=1201439002</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>714479</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 100 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81684</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>beclometasona</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>714441</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>BECLO-ASMA 50 MICROGRAMOS/PULSACION SOLUCION PARA INHALACION EN ENVASE A PRESION, 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 250-500 µg/12h
+D.màx: 1.000 µg/12h
+Asma baixa: 200-500 µg/24h
+Asma mitjana: 501-1.000 µg/24h
+Asma alta: 1.001-2.000 µg/24h</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=81667</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>663046</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO ALDO-UNION 500 microgramos SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 40 µg si cal
+D.màx: 240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr"/>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=70939</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P141" s="12" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>SABA/SAMA</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>salbutamol + bromuro ipratropio</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>757412</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>BROMURO DE IPRATROPIO/SALBUTAMOL GENETIC 0,5 MG/2,5 MG SOLUCION PARA INHALACION POR NEBULIZADOR, 20 ampollas</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 100-200/40 µg si cal
+D.màx: 200/240 µg/24h</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr"/>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=87927</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O142" s="12" t="inlineStr"/>
+      <c r="P142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>728863</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,25 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr"/>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85219</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O143" s="12" t="inlineStr"/>
+      <c r="P143" s="12" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>728864</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>BUDENA 0,5 MG/ML SUSPENSION PARA INHALACION POR NEBULIZADOR, 20 ampollas de 2 ml</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>NEB</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr"/>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=85220</t>
+        </is>
+      </c>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>NO INCORPORAR — nebulitzador</t>
+        </is>
+      </c>
+      <c r="O144" s="12" t="inlineStr"/>
+      <c r="P144" s="12" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>GCI</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>686770</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA PULMICTAN 200 microgramos/INHALACION SUSPENSION PARA INHALACION EN ENVASE A PRESION , 1 inhalador de 200 dosis</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 200-400 µg/12h
+D.màx: 800 µg/12h
+Asma baixa: 200-400 µg/24h
+Asma mitjana: 401-800 µg/24h
+Asma alta: 801-1.600 µg/24h</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>20-30 l/m</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
+        <is>
+          <t>Lenta</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11880</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=59035</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>723825</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 1 inhalador (60 dosis)</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>LABA/GCI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>budesonida + formoterol</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>731458</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>BUDESONIDA/FORMOTEROL CIPLA 160 MICROGRAMOS/4,5 MICROGRAMOS/INHALACION POLVO PARA INHALACION (UNIDOSIS), 2 inhaladores ( 2 x 60 dosis)</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>MPOC: 9/320 µg/12h
+D.màx: 36/1.280 µg/24h
+Asma baixa: 4.5/160 µg/12h
+Asma mitjana: 9/320 µg/12h
+Asma alta: 2 inh 9/320 µg/12h</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>IPS-uni</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>&lt;50 l/m</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11816</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=83517</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7048,17 +10880,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>COLUMNES AUTOMÀTIQUES (omplertes pel script)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7228,17 +11056,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>COLUMNES DE VALIDACIÓ CLÍNICA (les omples tu)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7264,17 +11088,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>COLORS DE FILES</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7324,17 +11144,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>QUAN EL SCRIPT DETECTA UN FÀRMAC NOU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
+++ b/inhaladors_MPOC_ASMA_Avanzado_FINAL.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z179"/>
+  <dimension ref="A1:Z180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="20.13" customWidth="1" style="28" min="1" max="1"/>
@@ -13112,6 +13112,81 @@
       </c>
       <c r="O179" s="29" t="inlineStr"/>
       <c r="P179" s="29" t="inlineStr"/>
+    </row>
+    <row r="180" ht="40" customHeight="1" s="28">
+      <c r="A180" s="29" t="inlineStr">
+        <is>
+          <t>LABA/LAMA</t>
+        </is>
+      </c>
+      <c r="B180" s="29" t="inlineStr">
+        <is>
+          <t>aclidinio + formoterol</t>
+        </is>
+      </c>
+      <c r="C180" s="29" t="inlineStr">
+        <is>
+          <t>BRIMICA GENUAIR 340 MICROGRAMOS/12 MICROGRAMOS POLVO PARA INHALACION, 60 dosis</t>
+        </is>
+      </c>
+      <c r="D180" s="29" t="inlineStr">
+        <is>
+          <t>770181</t>
+        </is>
+      </c>
+      <c r="E180" s="29" t="inlineStr">
+        <is>
+          <t>BRIMICA GENUAIR 340 MICROGRAMOS/12 MICROGRAMOS POLVO PARA INHALACION, 60 dosis</t>
+        </is>
+      </c>
+      <c r="F180" s="29" t="inlineStr">
+        <is>
+          <t>MPOC: 12/340 µg/12h
+D.màx: 12/340 µg/12h</t>
+        </is>
+      </c>
+      <c r="G180" s="29" t="inlineStr">
+        <is>
+          <t>IPS-multi</t>
+        </is>
+      </c>
+      <c r="H180" s="29" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I180" s="29" t="inlineStr">
+        <is>
+          <t>60-90 l/m</t>
+        </is>
+      </c>
+      <c r="J180" s="29" t="inlineStr">
+        <is>
+          <t>Ràpida</t>
+        </is>
+      </c>
+      <c r="K180" s="29" t="inlineStr">
+        <is>
+          <t>https://scientiasalut.gencat.cat/handle/11351/11878</t>
+        </is>
+      </c>
+      <c r="L180" s="29" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M180" s="29" t="inlineStr">
+        <is>
+          <t>https://cima.aemps.es/cima/publico/medicamento.html?nregistro=114963001IP</t>
+        </is>
+      </c>
+      <c r="N180" s="29" t="inlineStr">
+        <is>
+          <t>NOU — PENDENT VALIDACIÓ CLÍNICA</t>
+        </is>
+      </c>
+      <c r="O180" s="29" t="inlineStr"/>
+      <c r="P180" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$140"/>
